--- a/irrbb_calc/output/irrbb_shock_curves.xlsx
+++ b/irrbb_calc/output/irrbb_shock_curves.xlsx
@@ -1032,73 +1032,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.4612</v>
+        <v>5.4605</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9468520499999999</v>
+        <v>0.94685916</v>
       </c>
       <c r="F5" t="n">
         <v>250</v>
       </c>
       <c r="G5" t="n">
-        <v>7.9612</v>
+        <v>7.9605</v>
       </c>
       <c r="H5" t="n">
-        <v>0.92347419</v>
+        <v>0.92348112</v>
       </c>
       <c r="I5" t="n">
         <v>-250</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9612</v>
+        <v>2.9605</v>
       </c>
       <c r="K5" t="n">
-        <v>0.97082173</v>
+        <v>0.97082901</v>
       </c>
       <c r="L5" t="n">
         <v>1.64</v>
       </c>
       <c r="M5" t="n">
-        <v>5.4777</v>
+        <v>5.4769</v>
       </c>
       <c r="N5" t="n">
-        <v>0.94669643</v>
+        <v>0.94670354</v>
       </c>
       <c r="O5" t="n">
         <v>31.89</v>
       </c>
       <c r="P5" t="n">
-        <v>5.7802</v>
+        <v>5.7794</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9438371</v>
+        <v>0.94384418</v>
       </c>
       <c r="R5" t="n">
         <v>128.76</v>
       </c>
       <c r="S5" t="n">
-        <v>6.7488</v>
+        <v>6.7481</v>
       </c>
       <c r="T5" t="n">
-        <v>0.93473875</v>
+        <v>0.93474576</v>
       </c>
       <c r="U5" t="n">
         <v>-128.76</v>
       </c>
       <c r="V5" t="n">
-        <v>4.1737</v>
+        <v>4.1729</v>
       </c>
       <c r="W5" t="n">
-        <v>0.95912234</v>
+        <v>0.95912953</v>
       </c>
       <c r="X5" t="n">
         <v>-100</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.4612</v>
+        <v>4.4605</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.95636808</v>
+        <v>0.95637525</v>
       </c>
     </row>
     <row r="6">
@@ -1116,73 +1116,73 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>5.2819</v>
+        <v>5.1872</v>
       </c>
       <c r="E6" t="n">
-        <v>0.89975119</v>
+        <v>0.90145629</v>
       </c>
       <c r="F6" t="n">
         <v>250</v>
       </c>
       <c r="G6" t="n">
-        <v>7.7819</v>
+        <v>7.6872</v>
       </c>
       <c r="H6" t="n">
-        <v>0.85586981</v>
+        <v>0.8574917399999999</v>
       </c>
       <c r="I6" t="n">
         <v>-250</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7819</v>
+        <v>2.6872</v>
       </c>
       <c r="K6" t="n">
-        <v>0.94588242</v>
+        <v>0.94767494</v>
       </c>
       <c r="L6" t="n">
         <v>85.94</v>
       </c>
       <c r="M6" t="n">
-        <v>6.1413</v>
+        <v>6.0466</v>
       </c>
       <c r="N6" t="n">
-        <v>0.88441824</v>
+        <v>0.88609428</v>
       </c>
       <c r="O6" t="n">
         <v>-59.38</v>
       </c>
       <c r="P6" t="n">
-        <v>4.688</v>
+        <v>4.5934</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9105005</v>
+        <v>0.9122259700000001</v>
       </c>
       <c r="R6" t="n">
         <v>47.37</v>
       </c>
       <c r="S6" t="n">
-        <v>5.7555</v>
+        <v>5.6609</v>
       </c>
       <c r="T6" t="n">
-        <v>0.89126767</v>
+        <v>0.89295669</v>
       </c>
       <c r="U6" t="n">
         <v>-47.37</v>
       </c>
       <c r="V6" t="n">
-        <v>4.8082</v>
+        <v>4.7135</v>
       </c>
       <c r="W6" t="n">
-        <v>0.90831546</v>
+        <v>0.91003678</v>
       </c>
       <c r="X6" t="n">
         <v>-100</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.2819</v>
+        <v>4.1872</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.91792737</v>
+        <v>0.91966691</v>
       </c>
     </row>
     <row r="7">
@@ -1200,73 +1200,73 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>5.2818</v>
+        <v>5.1917</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8534610500000001</v>
+        <v>0.85577254</v>
       </c>
       <c r="F7" t="n">
         <v>250</v>
       </c>
       <c r="G7" t="n">
-        <v>7.7818</v>
+        <v>7.6917</v>
       </c>
       <c r="H7" t="n">
-        <v>0.79179293</v>
+        <v>0.7939374</v>
       </c>
       <c r="I7" t="n">
         <v>-250</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7818</v>
+        <v>2.6917</v>
       </c>
       <c r="K7" t="n">
-        <v>0.91993214</v>
+        <v>0.92242366</v>
       </c>
       <c r="L7" t="n">
         <v>116.95</v>
       </c>
       <c r="M7" t="n">
-        <v>6.4514</v>
+        <v>6.3612</v>
       </c>
       <c r="N7" t="n">
-        <v>0.82403603</v>
+        <v>0.82626782</v>
       </c>
       <c r="O7" t="n">
         <v>-92.95999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>4.3523</v>
+        <v>4.2621</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.87759699</v>
+        <v>0.8799738499999999</v>
       </c>
       <c r="R7" t="n">
         <v>17.43</v>
       </c>
       <c r="S7" t="n">
-        <v>5.4561</v>
+        <v>5.3659</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8490111</v>
+        <v>0.8513105399999999</v>
       </c>
       <c r="U7" t="n">
         <v>-17.43</v>
       </c>
       <c r="V7" t="n">
-        <v>5.1076</v>
+        <v>5.0174</v>
       </c>
       <c r="W7" t="n">
-        <v>0.85793432</v>
+        <v>0.8602579299999999</v>
       </c>
       <c r="X7" t="n">
         <v>-100</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.2818</v>
+        <v>4.1917</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.87945281</v>
+        <v>0.88183469</v>
       </c>
     </row>
     <row r="8">
@@ -1284,73 +1284,73 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>5.2806</v>
+        <v>5.1987</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7679489</v>
+        <v>0.77110321</v>
       </c>
       <c r="F8" t="n">
         <v>250</v>
       </c>
       <c r="G8" t="n">
-        <v>7.7806</v>
+        <v>7.6987</v>
       </c>
       <c r="H8" t="n">
-        <v>0.67771253</v>
+        <v>0.6804962</v>
       </c>
       <c r="I8" t="n">
         <v>-250</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7806</v>
+        <v>2.6987</v>
       </c>
       <c r="K8" t="n">
-        <v>0.87020011</v>
+        <v>0.87377441</v>
       </c>
       <c r="L8" t="n">
         <v>132.56</v>
       </c>
       <c r="M8" t="n">
-        <v>6.6062</v>
+        <v>6.5242</v>
       </c>
       <c r="N8" t="n">
-        <v>0.71870031</v>
+        <v>0.72165233</v>
       </c>
       <c r="O8" t="n">
         <v>-109.86</v>
       </c>
       <c r="P8" t="n">
-        <v>4.1821</v>
+        <v>4.1001</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.81131053</v>
+        <v>0.81464294</v>
       </c>
       <c r="R8" t="n">
         <v>2.36</v>
       </c>
       <c r="S8" t="n">
-        <v>5.3042</v>
+        <v>5.2222</v>
       </c>
       <c r="T8" t="n">
-        <v>0.76704392</v>
+        <v>0.7701945100000001</v>
       </c>
       <c r="U8" t="n">
         <v>-2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>5.2571</v>
+        <v>5.1751</v>
       </c>
       <c r="W8" t="n">
-        <v>0.76885496</v>
+        <v>0.77201299</v>
       </c>
       <c r="X8" t="n">
         <v>-100</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.2806</v>
+        <v>4.1987</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.80732249</v>
+        <v>0.81063852</v>
       </c>
     </row>
     <row r="9">
@@ -1368,73 +1368,73 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>5.2784</v>
+        <v>5.2036</v>
       </c>
       <c r="E9" t="n">
-        <v>0.69108987</v>
+        <v>0.69471757</v>
       </c>
       <c r="F9" t="n">
         <v>250</v>
       </c>
       <c r="G9" t="n">
-        <v>7.7784</v>
+        <v>7.7036</v>
       </c>
       <c r="H9" t="n">
-        <v>0.58014025</v>
+        <v>0.58318554</v>
       </c>
       <c r="I9" t="n">
         <v>-250</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7784</v>
+        <v>2.7036</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8232582000000001</v>
+        <v>0.82757968</v>
       </c>
       <c r="L9" t="n">
         <v>134.67</v>
       </c>
       <c r="M9" t="n">
-        <v>6.6251</v>
+        <v>6.5503</v>
       </c>
       <c r="N9" t="n">
-        <v>0.62891824</v>
+        <v>0.6322195900000001</v>
       </c>
       <c r="O9" t="n">
         <v>-112.14</v>
       </c>
       <c r="P9" t="n">
-        <v>4.1569</v>
+        <v>4.0821</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.74752619</v>
+        <v>0.75145013</v>
       </c>
       <c r="R9" t="n">
         <v>0.32</v>
       </c>
       <c r="S9" t="n">
-        <v>5.2816</v>
+        <v>5.2068</v>
       </c>
       <c r="T9" t="n">
-        <v>0.69093549</v>
+        <v>0.69456238</v>
       </c>
       <c r="U9" t="n">
         <v>-0.32</v>
       </c>
       <c r="V9" t="n">
-        <v>5.2752</v>
+        <v>5.2004</v>
       </c>
       <c r="W9" t="n">
-        <v>0.69124429</v>
+        <v>0.6948728</v>
       </c>
       <c r="X9" t="n">
         <v>-100</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.2784</v>
+        <v>4.2036</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.74119954</v>
+        <v>0.74509028</v>
       </c>
     </row>
     <row r="10">
@@ -1452,73 +1452,73 @@
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>5.2739</v>
+        <v>5.2083</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5901450499999999</v>
+        <v>0.59402774</v>
       </c>
       <c r="F10" t="n">
         <v>250</v>
       </c>
       <c r="G10" t="n">
-        <v>7.7739</v>
+        <v>7.7083</v>
       </c>
       <c r="H10" t="n">
-        <v>0.45960543</v>
+        <v>0.46262927</v>
       </c>
       <c r="I10" t="n">
         <v>-250</v>
       </c>
       <c r="J10" t="n">
-        <v>2.7739</v>
+        <v>2.7083</v>
       </c>
       <c r="K10" t="n">
-        <v>0.75776124</v>
+        <v>0.76274671</v>
       </c>
       <c r="L10" t="n">
         <v>134.98</v>
       </c>
       <c r="M10" t="n">
-        <v>6.6237</v>
+        <v>6.5581</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5156276</v>
+        <v>0.51902003</v>
       </c>
       <c r="O10" t="n">
         <v>-112.48</v>
       </c>
       <c r="P10" t="n">
-        <v>4.149</v>
+        <v>4.0835</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.66040318</v>
+        <v>0.6647481200000001</v>
       </c>
       <c r="R10" t="n">
         <v>0.02</v>
       </c>
       <c r="S10" t="n">
-        <v>5.274</v>
+        <v>5.2085</v>
       </c>
       <c r="T10" t="n">
-        <v>0.59013567</v>
+        <v>0.5940183</v>
       </c>
       <c r="U10" t="n">
         <v>-0.02</v>
       </c>
       <c r="V10" t="n">
-        <v>5.2737</v>
+        <v>5.2081</v>
       </c>
       <c r="W10" t="n">
-        <v>0.59015443</v>
+        <v>0.5940371800000001</v>
       </c>
       <c r="X10" t="n">
         <v>-100</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.2739</v>
+        <v>4.2083</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.65221114</v>
+        <v>0.65650218</v>
       </c>
     </row>
     <row r="11">
@@ -1536,73 +1536,73 @@
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>5.2655</v>
+        <v>5.212</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4539213</v>
+        <v>0.4575797</v>
       </c>
       <c r="F11" t="n">
         <v>250</v>
       </c>
       <c r="G11" t="n">
-        <v>7.7655</v>
+        <v>7.712</v>
       </c>
       <c r="H11" t="n">
-        <v>0.31197524</v>
+        <v>0.31448962</v>
       </c>
       <c r="I11" t="n">
         <v>-250</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7655</v>
+        <v>2.712</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6604516</v>
+        <v>0.66577454</v>
       </c>
       <c r="L11" t="n">
         <v>135</v>
       </c>
       <c r="M11" t="n">
-        <v>6.6155</v>
+        <v>6.562</v>
       </c>
       <c r="N11" t="n">
-        <v>0.37071145</v>
+        <v>0.37369922</v>
       </c>
       <c r="O11" t="n">
         <v>-112.5</v>
       </c>
       <c r="P11" t="n">
-        <v>4.1405</v>
+        <v>4.087</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5373629</v>
+        <v>0.5416938</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>5.2655</v>
+        <v>5.212</v>
       </c>
       <c r="T11" t="n">
-        <v>0.45392123</v>
+        <v>0.45757963</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>5.2655</v>
+        <v>5.212</v>
       </c>
       <c r="W11" t="n">
-        <v>0.45392138</v>
+        <v>0.45757978</v>
       </c>
       <c r="X11" t="n">
         <v>-100</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.2655</v>
+        <v>4.212</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.52738131</v>
+        <v>0.5316317699999999</v>
       </c>
     </row>
     <row r="12">
@@ -1620,73 +1620,73 @@
         <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>5.2577</v>
+        <v>5.2132</v>
       </c>
       <c r="E12" t="n">
-        <v>0.34939779</v>
+        <v>0.35252178</v>
       </c>
       <c r="F12" t="n">
         <v>250</v>
       </c>
       <c r="G12" t="n">
-        <v>7.7577</v>
+        <v>7.7132</v>
       </c>
       <c r="H12" t="n">
-        <v>0.21192047</v>
+        <v>0.21381527</v>
       </c>
       <c r="I12" t="n">
         <v>-250</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7577</v>
+        <v>2.7132</v>
       </c>
       <c r="K12" t="n">
-        <v>0.57605956</v>
+        <v>0.58121016</v>
       </c>
       <c r="L12" t="n">
         <v>135</v>
       </c>
       <c r="M12" t="n">
-        <v>6.6077</v>
+        <v>6.5632</v>
       </c>
       <c r="N12" t="n">
-        <v>0.26672311</v>
+        <v>0.2691079</v>
       </c>
       <c r="O12" t="n">
         <v>-112.5</v>
       </c>
       <c r="P12" t="n">
-        <v>4.1327</v>
+        <v>4.0882</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.43755878</v>
+        <v>0.44147103</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>5.2577</v>
+        <v>5.2132</v>
       </c>
       <c r="T12" t="n">
-        <v>0.34939779</v>
+        <v>0.35252178</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.2577</v>
+        <v>5.2132</v>
       </c>
       <c r="W12" t="n">
-        <v>0.34939779</v>
+        <v>0.35252178</v>
       </c>
       <c r="X12" t="n">
         <v>-100</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.2577</v>
+        <v>4.2132</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.42675542</v>
+        <v>0.43057108</v>
       </c>
     </row>
     <row r="13">
@@ -1704,73 +1704,73 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2454</v>
+        <v>5.213</v>
       </c>
       <c r="E13" t="n">
-        <v>0.20729198</v>
+        <v>0.20931663</v>
       </c>
       <c r="F13" t="n">
         <v>250</v>
       </c>
       <c r="G13" t="n">
-        <v>7.7454</v>
+        <v>7.713</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0979178</v>
+        <v>0.09887417</v>
       </c>
       <c r="I13" t="n">
         <v>-250</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7454</v>
+        <v>2.713</v>
       </c>
       <c r="K13" t="n">
-        <v>0.43883713</v>
+        <v>0.4431233</v>
       </c>
       <c r="L13" t="n">
         <v>135</v>
       </c>
       <c r="M13" t="n">
-        <v>6.5954</v>
+        <v>6.563</v>
       </c>
       <c r="N13" t="n">
-        <v>0.13825894</v>
+        <v>0.13960934</v>
       </c>
       <c r="O13" t="n">
         <v>-112.5</v>
       </c>
       <c r="P13" t="n">
-        <v>4.1204</v>
+        <v>4.088</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.29050719</v>
+        <v>0.29334461</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>5.2454</v>
+        <v>5.213</v>
       </c>
       <c r="T13" t="n">
-        <v>0.20729198</v>
+        <v>0.20931663</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>5.2454</v>
+        <v>5.213</v>
       </c>
       <c r="W13" t="n">
-        <v>0.20729198</v>
+        <v>0.20931663</v>
       </c>
       <c r="X13" t="n">
         <v>-100</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.2454</v>
+        <v>4.213</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.27981491</v>
+        <v>0.28254789</v>
       </c>
     </row>
     <row r="14">
@@ -2040,73 +2040,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.4612</v>
+        <v>5.4605</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9468520499999999</v>
+        <v>0.94685916</v>
       </c>
       <c r="F17" t="n">
         <v>250</v>
       </c>
       <c r="G17" t="n">
-        <v>7.9612</v>
+        <v>7.9605</v>
       </c>
       <c r="H17" t="n">
-        <v>0.92347419</v>
+        <v>0.92348112</v>
       </c>
       <c r="I17" t="n">
         <v>-250</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9612</v>
+        <v>2.9605</v>
       </c>
       <c r="K17" t="n">
-        <v>0.97082173</v>
+        <v>0.97082901</v>
       </c>
       <c r="L17" t="n">
         <v>1.64</v>
       </c>
       <c r="M17" t="n">
-        <v>5.4777</v>
+        <v>5.4769</v>
       </c>
       <c r="N17" t="n">
-        <v>0.94669643</v>
+        <v>0.94670354</v>
       </c>
       <c r="O17" t="n">
         <v>31.89</v>
       </c>
       <c r="P17" t="n">
-        <v>5.7802</v>
+        <v>5.7794</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9438371</v>
+        <v>0.94384418</v>
       </c>
       <c r="R17" t="n">
         <v>128.76</v>
       </c>
       <c r="S17" t="n">
-        <v>6.7488</v>
+        <v>6.7481</v>
       </c>
       <c r="T17" t="n">
-        <v>0.93473875</v>
+        <v>0.93474576</v>
       </c>
       <c r="U17" t="n">
         <v>-128.76</v>
       </c>
       <c r="V17" t="n">
-        <v>4.1737</v>
+        <v>4.1729</v>
       </c>
       <c r="W17" t="n">
-        <v>0.95912234</v>
+        <v>0.95912953</v>
       </c>
       <c r="X17" t="n">
         <v>-100</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.4612</v>
+        <v>4.4605</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.95636808</v>
+        <v>0.95637525</v>
       </c>
     </row>
     <row r="18">
@@ -2124,73 +2124,73 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>5.2819</v>
+        <v>5.1872</v>
       </c>
       <c r="E18" t="n">
-        <v>0.89975119</v>
+        <v>0.90145629</v>
       </c>
       <c r="F18" t="n">
         <v>250</v>
       </c>
       <c r="G18" t="n">
-        <v>7.7819</v>
+        <v>7.6872</v>
       </c>
       <c r="H18" t="n">
-        <v>0.85586981</v>
+        <v>0.8574917399999999</v>
       </c>
       <c r="I18" t="n">
         <v>-250</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7819</v>
+        <v>2.6872</v>
       </c>
       <c r="K18" t="n">
-        <v>0.94588242</v>
+        <v>0.94767494</v>
       </c>
       <c r="L18" t="n">
         <v>85.94</v>
       </c>
       <c r="M18" t="n">
-        <v>6.1413</v>
+        <v>6.0466</v>
       </c>
       <c r="N18" t="n">
-        <v>0.88441824</v>
+        <v>0.88609428</v>
       </c>
       <c r="O18" t="n">
         <v>-59.38</v>
       </c>
       <c r="P18" t="n">
-        <v>4.688</v>
+        <v>4.5934</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9105005</v>
+        <v>0.9122259700000001</v>
       </c>
       <c r="R18" t="n">
         <v>47.37</v>
       </c>
       <c r="S18" t="n">
-        <v>5.7555</v>
+        <v>5.6609</v>
       </c>
       <c r="T18" t="n">
-        <v>0.89126767</v>
+        <v>0.89295669</v>
       </c>
       <c r="U18" t="n">
         <v>-47.37</v>
       </c>
       <c r="V18" t="n">
-        <v>4.8082</v>
+        <v>4.7135</v>
       </c>
       <c r="W18" t="n">
-        <v>0.90831546</v>
+        <v>0.91003678</v>
       </c>
       <c r="X18" t="n">
         <v>-100</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.2819</v>
+        <v>4.1872</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.91792737</v>
+        <v>0.91966691</v>
       </c>
     </row>
     <row r="19">
@@ -2208,73 +2208,73 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>5.2818</v>
+        <v>5.1917</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8534610500000001</v>
+        <v>0.85577254</v>
       </c>
       <c r="F19" t="n">
         <v>250</v>
       </c>
       <c r="G19" t="n">
-        <v>7.7818</v>
+        <v>7.6917</v>
       </c>
       <c r="H19" t="n">
-        <v>0.79179293</v>
+        <v>0.7939374</v>
       </c>
       <c r="I19" t="n">
         <v>-250</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7818</v>
+        <v>2.6917</v>
       </c>
       <c r="K19" t="n">
-        <v>0.91993214</v>
+        <v>0.92242366</v>
       </c>
       <c r="L19" t="n">
         <v>116.95</v>
       </c>
       <c r="M19" t="n">
-        <v>6.4514</v>
+        <v>6.3612</v>
       </c>
       <c r="N19" t="n">
-        <v>0.82403603</v>
+        <v>0.82626782</v>
       </c>
       <c r="O19" t="n">
         <v>-92.95999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>4.3523</v>
+        <v>4.2621</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.87759699</v>
+        <v>0.8799738499999999</v>
       </c>
       <c r="R19" t="n">
         <v>17.43</v>
       </c>
       <c r="S19" t="n">
-        <v>5.4561</v>
+        <v>5.3659</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8490111</v>
+        <v>0.8513105399999999</v>
       </c>
       <c r="U19" t="n">
         <v>-17.43</v>
       </c>
       <c r="V19" t="n">
-        <v>5.1076</v>
+        <v>5.0174</v>
       </c>
       <c r="W19" t="n">
-        <v>0.85793432</v>
+        <v>0.8602579299999999</v>
       </c>
       <c r="X19" t="n">
         <v>-100</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.2818</v>
+        <v>4.1917</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.87945281</v>
+        <v>0.88183469</v>
       </c>
     </row>
     <row r="20">
@@ -2292,73 +2292,73 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>5.2806</v>
+        <v>5.1987</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7679489</v>
+        <v>0.77110321</v>
       </c>
       <c r="F20" t="n">
         <v>250</v>
       </c>
       <c r="G20" t="n">
-        <v>7.7806</v>
+        <v>7.6987</v>
       </c>
       <c r="H20" t="n">
-        <v>0.67771253</v>
+        <v>0.6804962</v>
       </c>
       <c r="I20" t="n">
         <v>-250</v>
       </c>
       <c r="J20" t="n">
-        <v>2.7806</v>
+        <v>2.6987</v>
       </c>
       <c r="K20" t="n">
-        <v>0.87020011</v>
+        <v>0.87377441</v>
       </c>
       <c r="L20" t="n">
         <v>132.56</v>
       </c>
       <c r="M20" t="n">
-        <v>6.6062</v>
+        <v>6.5242</v>
       </c>
       <c r="N20" t="n">
-        <v>0.71870031</v>
+        <v>0.72165233</v>
       </c>
       <c r="O20" t="n">
         <v>-109.86</v>
       </c>
       <c r="P20" t="n">
-        <v>4.1821</v>
+        <v>4.1001</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.81131053</v>
+        <v>0.81464294</v>
       </c>
       <c r="R20" t="n">
         <v>2.36</v>
       </c>
       <c r="S20" t="n">
-        <v>5.3042</v>
+        <v>5.2222</v>
       </c>
       <c r="T20" t="n">
-        <v>0.76704392</v>
+        <v>0.7701945100000001</v>
       </c>
       <c r="U20" t="n">
         <v>-2.36</v>
       </c>
       <c r="V20" t="n">
-        <v>5.2571</v>
+        <v>5.1751</v>
       </c>
       <c r="W20" t="n">
-        <v>0.76885496</v>
+        <v>0.77201299</v>
       </c>
       <c r="X20" t="n">
         <v>-100</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.2806</v>
+        <v>4.1987</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.80732249</v>
+        <v>0.81063852</v>
       </c>
     </row>
     <row r="21">
@@ -2376,73 +2376,73 @@
         <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>5.2784</v>
+        <v>5.2036</v>
       </c>
       <c r="E21" t="n">
-        <v>0.69108987</v>
+        <v>0.69471757</v>
       </c>
       <c r="F21" t="n">
         <v>250</v>
       </c>
       <c r="G21" t="n">
-        <v>7.7784</v>
+        <v>7.7036</v>
       </c>
       <c r="H21" t="n">
-        <v>0.58014025</v>
+        <v>0.58318554</v>
       </c>
       <c r="I21" t="n">
         <v>-250</v>
       </c>
       <c r="J21" t="n">
-        <v>2.7784</v>
+        <v>2.7036</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8232582000000001</v>
+        <v>0.82757968</v>
       </c>
       <c r="L21" t="n">
         <v>134.67</v>
       </c>
       <c r="M21" t="n">
-        <v>6.6251</v>
+        <v>6.5503</v>
       </c>
       <c r="N21" t="n">
-        <v>0.62891824</v>
+        <v>0.6322195900000001</v>
       </c>
       <c r="O21" t="n">
         <v>-112.14</v>
       </c>
       <c r="P21" t="n">
-        <v>4.1569</v>
+        <v>4.0821</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.74752619</v>
+        <v>0.75145013</v>
       </c>
       <c r="R21" t="n">
         <v>0.32</v>
       </c>
       <c r="S21" t="n">
-        <v>5.2816</v>
+        <v>5.2068</v>
       </c>
       <c r="T21" t="n">
-        <v>0.69093549</v>
+        <v>0.69456238</v>
       </c>
       <c r="U21" t="n">
         <v>-0.32</v>
       </c>
       <c r="V21" t="n">
-        <v>5.2752</v>
+        <v>5.2004</v>
       </c>
       <c r="W21" t="n">
-        <v>0.69124429</v>
+        <v>0.6948728</v>
       </c>
       <c r="X21" t="n">
         <v>-100</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.2784</v>
+        <v>4.2036</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.74119954</v>
+        <v>0.74509028</v>
       </c>
     </row>
     <row r="22">
@@ -2460,73 +2460,73 @@
         <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>5.2739</v>
+        <v>5.2083</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5901450499999999</v>
+        <v>0.59402774</v>
       </c>
       <c r="F22" t="n">
         <v>250</v>
       </c>
       <c r="G22" t="n">
-        <v>7.7739</v>
+        <v>7.7083</v>
       </c>
       <c r="H22" t="n">
-        <v>0.45960543</v>
+        <v>0.46262927</v>
       </c>
       <c r="I22" t="n">
         <v>-250</v>
       </c>
       <c r="J22" t="n">
-        <v>2.7739</v>
+        <v>2.7083</v>
       </c>
       <c r="K22" t="n">
-        <v>0.75776124</v>
+        <v>0.76274671</v>
       </c>
       <c r="L22" t="n">
         <v>134.98</v>
       </c>
       <c r="M22" t="n">
-        <v>6.6237</v>
+        <v>6.5581</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5156276</v>
+        <v>0.51902003</v>
       </c>
       <c r="O22" t="n">
         <v>-112.48</v>
       </c>
       <c r="P22" t="n">
-        <v>4.149</v>
+        <v>4.0835</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.66040318</v>
+        <v>0.6647481200000001</v>
       </c>
       <c r="R22" t="n">
         <v>0.02</v>
       </c>
       <c r="S22" t="n">
-        <v>5.274</v>
+        <v>5.2085</v>
       </c>
       <c r="T22" t="n">
-        <v>0.59013567</v>
+        <v>0.5940183</v>
       </c>
       <c r="U22" t="n">
         <v>-0.02</v>
       </c>
       <c r="V22" t="n">
-        <v>5.2737</v>
+        <v>5.2081</v>
       </c>
       <c r="W22" t="n">
-        <v>0.59015443</v>
+        <v>0.5940371800000001</v>
       </c>
       <c r="X22" t="n">
         <v>-100</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.2739</v>
+        <v>4.2083</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.65221114</v>
+        <v>0.65650218</v>
       </c>
     </row>
     <row r="23">
@@ -2544,73 +2544,73 @@
         <v>15</v>
       </c>
       <c r="D23" t="n">
-        <v>5.2655</v>
+        <v>5.212</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4539213</v>
+        <v>0.4575797</v>
       </c>
       <c r="F23" t="n">
         <v>250</v>
       </c>
       <c r="G23" t="n">
-        <v>7.7655</v>
+        <v>7.712</v>
       </c>
       <c r="H23" t="n">
-        <v>0.31197524</v>
+        <v>0.31448962</v>
       </c>
       <c r="I23" t="n">
         <v>-250</v>
       </c>
       <c r="J23" t="n">
-        <v>2.7655</v>
+        <v>2.712</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6604516</v>
+        <v>0.66577454</v>
       </c>
       <c r="L23" t="n">
         <v>135</v>
       </c>
       <c r="M23" t="n">
-        <v>6.6155</v>
+        <v>6.562</v>
       </c>
       <c r="N23" t="n">
-        <v>0.37071145</v>
+        <v>0.37369922</v>
       </c>
       <c r="O23" t="n">
         <v>-112.5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.1405</v>
+        <v>4.087</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.5373629</v>
+        <v>0.5416938</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>5.2655</v>
+        <v>5.212</v>
       </c>
       <c r="T23" t="n">
-        <v>0.45392123</v>
+        <v>0.45757963</v>
       </c>
       <c r="U23" t="n">
         <v>-0</v>
       </c>
       <c r="V23" t="n">
-        <v>5.2655</v>
+        <v>5.212</v>
       </c>
       <c r="W23" t="n">
-        <v>0.45392138</v>
+        <v>0.45757978</v>
       </c>
       <c r="X23" t="n">
         <v>-100</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.2655</v>
+        <v>4.212</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.52738131</v>
+        <v>0.5316317699999999</v>
       </c>
     </row>
     <row r="24">
@@ -2628,73 +2628,73 @@
         <v>20</v>
       </c>
       <c r="D24" t="n">
-        <v>5.2577</v>
+        <v>5.2132</v>
       </c>
       <c r="E24" t="n">
-        <v>0.34939779</v>
+        <v>0.35252178</v>
       </c>
       <c r="F24" t="n">
         <v>250</v>
       </c>
       <c r="G24" t="n">
-        <v>7.7577</v>
+        <v>7.7132</v>
       </c>
       <c r="H24" t="n">
-        <v>0.21192047</v>
+        <v>0.21381527</v>
       </c>
       <c r="I24" t="n">
         <v>-250</v>
       </c>
       <c r="J24" t="n">
-        <v>2.7577</v>
+        <v>2.7132</v>
       </c>
       <c r="K24" t="n">
-        <v>0.57605956</v>
+        <v>0.58121016</v>
       </c>
       <c r="L24" t="n">
         <v>135</v>
       </c>
       <c r="M24" t="n">
-        <v>6.6077</v>
+        <v>6.5632</v>
       </c>
       <c r="N24" t="n">
-        <v>0.26672311</v>
+        <v>0.2691079</v>
       </c>
       <c r="O24" t="n">
         <v>-112.5</v>
       </c>
       <c r="P24" t="n">
-        <v>4.1327</v>
+        <v>4.0882</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.43755878</v>
+        <v>0.44147103</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>5.2577</v>
+        <v>5.2132</v>
       </c>
       <c r="T24" t="n">
-        <v>0.34939779</v>
+        <v>0.35252178</v>
       </c>
       <c r="U24" t="n">
         <v>-0</v>
       </c>
       <c r="V24" t="n">
-        <v>5.2577</v>
+        <v>5.2132</v>
       </c>
       <c r="W24" t="n">
-        <v>0.34939779</v>
+        <v>0.35252178</v>
       </c>
       <c r="X24" t="n">
         <v>-100</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.2577</v>
+        <v>4.2132</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.42675542</v>
+        <v>0.43057108</v>
       </c>
     </row>
     <row r="25">
@@ -2712,73 +2712,73 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>5.2454</v>
+        <v>5.213</v>
       </c>
       <c r="E25" t="n">
-        <v>0.20729198</v>
+        <v>0.20931663</v>
       </c>
       <c r="F25" t="n">
         <v>250</v>
       </c>
       <c r="G25" t="n">
-        <v>7.7454</v>
+        <v>7.713</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0979178</v>
+        <v>0.09887417</v>
       </c>
       <c r="I25" t="n">
         <v>-250</v>
       </c>
       <c r="J25" t="n">
-        <v>2.7454</v>
+        <v>2.713</v>
       </c>
       <c r="K25" t="n">
-        <v>0.43883713</v>
+        <v>0.4431233</v>
       </c>
       <c r="L25" t="n">
         <v>135</v>
       </c>
       <c r="M25" t="n">
-        <v>6.5954</v>
+        <v>6.563</v>
       </c>
       <c r="N25" t="n">
-        <v>0.13825894</v>
+        <v>0.13960934</v>
       </c>
       <c r="O25" t="n">
         <v>-112.5</v>
       </c>
       <c r="P25" t="n">
-        <v>4.1204</v>
+        <v>4.088</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.29050719</v>
+        <v>0.29334461</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>5.2454</v>
+        <v>5.213</v>
       </c>
       <c r="T25" t="n">
-        <v>0.20729198</v>
+        <v>0.20931663</v>
       </c>
       <c r="U25" t="n">
         <v>-0</v>
       </c>
       <c r="V25" t="n">
-        <v>5.2454</v>
+        <v>5.213</v>
       </c>
       <c r="W25" t="n">
-        <v>0.20729198</v>
+        <v>0.20931663</v>
       </c>
       <c r="X25" t="n">
         <v>-100</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.2454</v>
+        <v>4.213</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.27981491</v>
+        <v>0.28254789</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/irrbb_shock_curves.xlsx
+++ b/irrbb_calc/output/irrbb_shock_curves.xlsx
@@ -1032,73 +1032,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.4605</v>
+        <v>5.4616</v>
       </c>
       <c r="E5" t="n">
-        <v>0.94685916</v>
+        <v>0.94684891</v>
       </c>
       <c r="F5" t="n">
         <v>250</v>
       </c>
       <c r="G5" t="n">
-        <v>7.9605</v>
+        <v>7.9616</v>
       </c>
       <c r="H5" t="n">
-        <v>0.92348112</v>
+        <v>0.92347113</v>
       </c>
       <c r="I5" t="n">
         <v>-250</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9605</v>
+        <v>2.9616</v>
       </c>
       <c r="K5" t="n">
-        <v>0.97082901</v>
+        <v>0.97081851</v>
       </c>
       <c r="L5" t="n">
         <v>1.64</v>
       </c>
       <c r="M5" t="n">
-        <v>5.4769</v>
+        <v>5.478</v>
       </c>
       <c r="N5" t="n">
-        <v>0.94670354</v>
+        <v>0.94669329</v>
       </c>
       <c r="O5" t="n">
         <v>31.89</v>
       </c>
       <c r="P5" t="n">
-        <v>5.7794</v>
+        <v>5.7805</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.94384418</v>
+        <v>0.94383397</v>
       </c>
       <c r="R5" t="n">
         <v>128.76</v>
       </c>
       <c r="S5" t="n">
-        <v>6.7481</v>
+        <v>6.7492</v>
       </c>
       <c r="T5" t="n">
-        <v>0.93474576</v>
+        <v>0.93473564</v>
       </c>
       <c r="U5" t="n">
         <v>-128.76</v>
       </c>
       <c r="V5" t="n">
-        <v>4.1729</v>
+        <v>4.174</v>
       </c>
       <c r="W5" t="n">
-        <v>0.95912953</v>
+        <v>0.95911916</v>
       </c>
       <c r="X5" t="n">
         <v>-100</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.4605</v>
+        <v>4.4616</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.95637525</v>
+        <v>0.9563649</v>
       </c>
     </row>
     <row r="6">
@@ -1116,73 +1116,73 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>5.1872</v>
+        <v>5.3237</v>
       </c>
       <c r="E6" t="n">
-        <v>0.90145629</v>
+        <v>0.89899778</v>
       </c>
       <c r="F6" t="n">
         <v>250</v>
       </c>
       <c r="G6" t="n">
-        <v>7.6872</v>
+        <v>7.8237</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8574917399999999</v>
+        <v>0.85515314</v>
       </c>
       <c r="I6" t="n">
         <v>-250</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6872</v>
+        <v>2.8237</v>
       </c>
       <c r="K6" t="n">
-        <v>0.94767494</v>
+        <v>0.94509038</v>
       </c>
       <c r="L6" t="n">
         <v>85.94</v>
       </c>
       <c r="M6" t="n">
-        <v>6.0466</v>
+        <v>6.1831</v>
       </c>
       <c r="N6" t="n">
-        <v>0.88609428</v>
+        <v>0.88367767</v>
       </c>
       <c r="O6" t="n">
         <v>-59.38</v>
       </c>
       <c r="P6" t="n">
-        <v>4.5934</v>
+        <v>4.7299</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9122259700000001</v>
+        <v>0.9097380900000001</v>
       </c>
       <c r="R6" t="n">
         <v>47.37</v>
       </c>
       <c r="S6" t="n">
-        <v>5.6609</v>
+        <v>5.7974</v>
       </c>
       <c r="T6" t="n">
-        <v>0.89295669</v>
+        <v>0.89052136</v>
       </c>
       <c r="U6" t="n">
         <v>-47.37</v>
       </c>
       <c r="V6" t="n">
-        <v>4.7135</v>
+        <v>4.8501</v>
       </c>
       <c r="W6" t="n">
-        <v>0.91003678</v>
+        <v>0.90755487</v>
       </c>
       <c r="X6" t="n">
         <v>-100</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1872</v>
+        <v>4.3237</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.91966691</v>
+        <v>0.91715874</v>
       </c>
     </row>
     <row r="7">
@@ -1200,73 +1200,73 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>5.1917</v>
+        <v>5.3217</v>
       </c>
       <c r="E7" t="n">
-        <v>0.85577254</v>
+        <v>0.8524403</v>
       </c>
       <c r="F7" t="n">
         <v>250</v>
       </c>
       <c r="G7" t="n">
-        <v>7.6917</v>
+        <v>7.8217</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7939374</v>
+        <v>0.79084593</v>
       </c>
       <c r="I7" t="n">
         <v>-250</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6917</v>
+        <v>2.8217</v>
       </c>
       <c r="K7" t="n">
-        <v>0.92242366</v>
+        <v>0.91883189</v>
       </c>
       <c r="L7" t="n">
         <v>116.95</v>
       </c>
       <c r="M7" t="n">
-        <v>6.3612</v>
+        <v>6.4913</v>
       </c>
       <c r="N7" t="n">
-        <v>0.82626782</v>
+        <v>0.82305047</v>
       </c>
       <c r="O7" t="n">
         <v>-92.95999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>4.2621</v>
+        <v>4.3922</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8799738499999999</v>
+        <v>0.87654737</v>
       </c>
       <c r="R7" t="n">
         <v>17.43</v>
       </c>
       <c r="S7" t="n">
-        <v>5.3659</v>
+        <v>5.496</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8513105399999999</v>
+        <v>0.84799567</v>
       </c>
       <c r="U7" t="n">
         <v>-17.43</v>
       </c>
       <c r="V7" t="n">
-        <v>5.0174</v>
+        <v>5.1475</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8602579299999999</v>
+        <v>0.85690822</v>
       </c>
       <c r="X7" t="n">
         <v>-100</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.1917</v>
+        <v>4.3217</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.88183469</v>
+        <v>0.8784009699999999</v>
       </c>
     </row>
     <row r="8">
@@ -1284,73 +1284,73 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>5.1987</v>
+        <v>5.3169</v>
       </c>
       <c r="E8" t="n">
-        <v>0.77110321</v>
+        <v>0.76655736</v>
       </c>
       <c r="F8" t="n">
         <v>250</v>
       </c>
       <c r="G8" t="n">
-        <v>7.6987</v>
+        <v>7.8169</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6804962</v>
+        <v>0.6764845</v>
       </c>
       <c r="I8" t="n">
         <v>-250</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6987</v>
+        <v>2.8169</v>
       </c>
       <c r="K8" t="n">
-        <v>0.87377441</v>
+        <v>0.86862329</v>
       </c>
       <c r="L8" t="n">
         <v>132.56</v>
       </c>
       <c r="M8" t="n">
-        <v>6.5242</v>
+        <v>6.6425</v>
       </c>
       <c r="N8" t="n">
-        <v>0.72165233</v>
+        <v>0.717398</v>
       </c>
       <c r="O8" t="n">
         <v>-109.86</v>
       </c>
       <c r="P8" t="n">
-        <v>4.1001</v>
+        <v>4.2184</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.81464294</v>
+        <v>0.80984041</v>
       </c>
       <c r="R8" t="n">
         <v>2.36</v>
       </c>
       <c r="S8" t="n">
-        <v>5.2222</v>
+        <v>5.3405</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7701945100000001</v>
+        <v>0.76565402</v>
       </c>
       <c r="U8" t="n">
         <v>-2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>5.1751</v>
+        <v>5.2933</v>
       </c>
       <c r="W8" t="n">
-        <v>0.77201299</v>
+        <v>0.76746177</v>
       </c>
       <c r="X8" t="n">
         <v>-100</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.1987</v>
+        <v>4.3169</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.81063852</v>
+        <v>0.8058596</v>
       </c>
     </row>
     <row r="9">
@@ -1368,73 +1368,73 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>5.2036</v>
+        <v>5.3115</v>
       </c>
       <c r="E9" t="n">
-        <v>0.69471757</v>
+        <v>0.6894908</v>
       </c>
       <c r="F9" t="n">
         <v>250</v>
       </c>
       <c r="G9" t="n">
-        <v>7.7036</v>
+        <v>7.8115</v>
       </c>
       <c r="H9" t="n">
-        <v>0.58318554</v>
+        <v>0.5787979</v>
       </c>
       <c r="I9" t="n">
         <v>-250</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7036</v>
+        <v>2.8115</v>
       </c>
       <c r="K9" t="n">
-        <v>0.82757968</v>
+        <v>0.82135331</v>
       </c>
       <c r="L9" t="n">
         <v>134.67</v>
       </c>
       <c r="M9" t="n">
-        <v>6.5503</v>
+        <v>6.6582</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6322195900000001</v>
+        <v>0.62746303</v>
       </c>
       <c r="O9" t="n">
         <v>-112.14</v>
       </c>
       <c r="P9" t="n">
-        <v>4.0821</v>
+        <v>4.19</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.75145013</v>
+        <v>0.74579653</v>
       </c>
       <c r="R9" t="n">
         <v>0.32</v>
       </c>
       <c r="S9" t="n">
-        <v>5.2068</v>
+        <v>5.3146</v>
       </c>
       <c r="T9" t="n">
-        <v>0.69456238</v>
+        <v>0.68933678</v>
       </c>
       <c r="U9" t="n">
         <v>-0.32</v>
       </c>
       <c r="V9" t="n">
-        <v>5.2004</v>
+        <v>5.3083</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6948728</v>
+        <v>0.68964486</v>
       </c>
       <c r="X9" t="n">
         <v>-100</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.2036</v>
+        <v>4.3115</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.74509028</v>
+        <v>0.73948453</v>
       </c>
     </row>
     <row r="10">
@@ -1452,73 +1452,73 @@
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>5.2083</v>
+        <v>5.3029</v>
       </c>
       <c r="E10" t="n">
-        <v>0.59402774</v>
+        <v>0.58843521</v>
       </c>
       <c r="F10" t="n">
         <v>250</v>
       </c>
       <c r="G10" t="n">
-        <v>7.7083</v>
+        <v>7.8029</v>
       </c>
       <c r="H10" t="n">
-        <v>0.46262927</v>
+        <v>0.45827381</v>
       </c>
       <c r="I10" t="n">
         <v>-250</v>
       </c>
       <c r="J10" t="n">
-        <v>2.7083</v>
+        <v>2.8029</v>
       </c>
       <c r="K10" t="n">
-        <v>0.76274671</v>
+        <v>0.75556577</v>
       </c>
       <c r="L10" t="n">
         <v>134.98</v>
       </c>
       <c r="M10" t="n">
-        <v>6.5581</v>
+        <v>6.6527</v>
       </c>
       <c r="N10" t="n">
-        <v>0.51902003</v>
+        <v>0.51413367</v>
       </c>
       <c r="O10" t="n">
         <v>-112.48</v>
       </c>
       <c r="P10" t="n">
-        <v>4.0835</v>
+        <v>4.1781</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6647481200000001</v>
+        <v>0.65848979</v>
       </c>
       <c r="R10" t="n">
         <v>0.02</v>
       </c>
       <c r="S10" t="n">
-        <v>5.2085</v>
+        <v>5.303</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5940183</v>
+        <v>0.58842586</v>
       </c>
       <c r="U10" t="n">
         <v>-0.02</v>
       </c>
       <c r="V10" t="n">
-        <v>5.2081</v>
+        <v>5.3027</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5940371800000001</v>
+        <v>0.58844456</v>
       </c>
       <c r="X10" t="n">
         <v>-100</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.2083</v>
+        <v>4.3029</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.65650218</v>
+        <v>0.6503214899999999</v>
       </c>
     </row>
     <row r="11">
@@ -1536,73 +1536,73 @@
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>5.212</v>
+        <v>5.2892</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4575797</v>
+        <v>0.45231195</v>
       </c>
       <c r="F11" t="n">
         <v>250</v>
       </c>
       <c r="G11" t="n">
-        <v>7.712</v>
+        <v>7.7892</v>
       </c>
       <c r="H11" t="n">
-        <v>0.31448962</v>
+        <v>0.31086915</v>
       </c>
       <c r="I11" t="n">
         <v>-250</v>
       </c>
       <c r="J11" t="n">
-        <v>2.712</v>
+        <v>2.7892</v>
       </c>
       <c r="K11" t="n">
-        <v>0.66577454</v>
+        <v>0.65811</v>
       </c>
       <c r="L11" t="n">
         <v>135</v>
       </c>
       <c r="M11" t="n">
-        <v>6.562</v>
+        <v>6.6392</v>
       </c>
       <c r="N11" t="n">
-        <v>0.37369922</v>
+        <v>0.36939711</v>
       </c>
       <c r="O11" t="n">
         <v>-112.5</v>
       </c>
       <c r="P11" t="n">
-        <v>4.087</v>
+        <v>4.1642</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5416938</v>
+        <v>0.53545771</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>5.212</v>
+        <v>5.2892</v>
       </c>
       <c r="T11" t="n">
-        <v>0.45757963</v>
+        <v>0.45231187</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>5.212</v>
+        <v>5.2892</v>
       </c>
       <c r="W11" t="n">
-        <v>0.45757978</v>
+        <v>0.45231202</v>
       </c>
       <c r="X11" t="n">
         <v>-100</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.212</v>
+        <v>4.2892</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.5316317699999999</v>
+        <v>0.52551151</v>
       </c>
     </row>
     <row r="12">
@@ -1620,73 +1620,73 @@
         <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>5.2132</v>
+        <v>5.2774</v>
       </c>
       <c r="E12" t="n">
-        <v>0.35252178</v>
+        <v>0.34802439</v>
       </c>
       <c r="F12" t="n">
         <v>250</v>
       </c>
       <c r="G12" t="n">
-        <v>7.7132</v>
+        <v>7.7774</v>
       </c>
       <c r="H12" t="n">
-        <v>0.21381527</v>
+        <v>0.21108746</v>
       </c>
       <c r="I12" t="n">
         <v>-250</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7132</v>
+        <v>2.7774</v>
       </c>
       <c r="K12" t="n">
-        <v>0.58121016</v>
+        <v>0.57379521</v>
       </c>
       <c r="L12" t="n">
         <v>135</v>
       </c>
       <c r="M12" t="n">
-        <v>6.5632</v>
+        <v>6.6274</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2691079</v>
+        <v>0.26567468</v>
       </c>
       <c r="O12" t="n">
         <v>-112.5</v>
       </c>
       <c r="P12" t="n">
-        <v>4.0882</v>
+        <v>4.1524</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.44147103</v>
+        <v>0.43583884</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>5.2132</v>
+        <v>5.2774</v>
       </c>
       <c r="T12" t="n">
-        <v>0.35252178</v>
+        <v>0.34802439</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.2132</v>
+        <v>5.2774</v>
       </c>
       <c r="W12" t="n">
-        <v>0.35252178</v>
+        <v>0.34802439</v>
       </c>
       <c r="X12" t="n">
         <v>-100</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.2132</v>
+        <v>4.2774</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.43057108</v>
+        <v>0.42507795</v>
       </c>
     </row>
     <row r="13">
@@ -1704,73 +1704,73 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>5.213</v>
+        <v>5.2598</v>
       </c>
       <c r="E13" t="n">
-        <v>0.20931663</v>
+        <v>0.20640241</v>
       </c>
       <c r="F13" t="n">
         <v>250</v>
       </c>
       <c r="G13" t="n">
-        <v>7.713</v>
+        <v>7.7598</v>
       </c>
       <c r="H13" t="n">
-        <v>0.09887417</v>
+        <v>0.0974976</v>
       </c>
       <c r="I13" t="n">
         <v>-250</v>
       </c>
       <c r="J13" t="n">
-        <v>2.713</v>
+        <v>2.7598</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4431233</v>
+        <v>0.43695391</v>
       </c>
       <c r="L13" t="n">
         <v>135</v>
       </c>
       <c r="M13" t="n">
-        <v>6.563</v>
+        <v>6.6098</v>
       </c>
       <c r="N13" t="n">
-        <v>0.13960934</v>
+        <v>0.13766562</v>
       </c>
       <c r="O13" t="n">
         <v>-112.5</v>
       </c>
       <c r="P13" t="n">
-        <v>4.088</v>
+        <v>4.1348</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.29334461</v>
+        <v>0.28926052</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>5.213</v>
+        <v>5.2598</v>
       </c>
       <c r="T13" t="n">
-        <v>0.20931663</v>
+        <v>0.20640241</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>5.213</v>
+        <v>5.2598</v>
       </c>
       <c r="W13" t="n">
-        <v>0.20931663</v>
+        <v>0.20640241</v>
       </c>
       <c r="X13" t="n">
         <v>-100</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.213</v>
+        <v>4.2598</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.28254789</v>
+        <v>0.27861412</v>
       </c>
     </row>
     <row r="14">
@@ -2040,73 +2040,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.4605</v>
+        <v>5.4616</v>
       </c>
       <c r="E17" t="n">
-        <v>0.94685916</v>
+        <v>0.94684891</v>
       </c>
       <c r="F17" t="n">
         <v>250</v>
       </c>
       <c r="G17" t="n">
-        <v>7.9605</v>
+        <v>7.9616</v>
       </c>
       <c r="H17" t="n">
-        <v>0.92348112</v>
+        <v>0.92347113</v>
       </c>
       <c r="I17" t="n">
         <v>-250</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9605</v>
+        <v>2.9616</v>
       </c>
       <c r="K17" t="n">
-        <v>0.97082901</v>
+        <v>0.97081851</v>
       </c>
       <c r="L17" t="n">
         <v>1.64</v>
       </c>
       <c r="M17" t="n">
-        <v>5.4769</v>
+        <v>5.478</v>
       </c>
       <c r="N17" t="n">
-        <v>0.94670354</v>
+        <v>0.94669329</v>
       </c>
       <c r="O17" t="n">
         <v>31.89</v>
       </c>
       <c r="P17" t="n">
-        <v>5.7794</v>
+        <v>5.7805</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.94384418</v>
+        <v>0.94383397</v>
       </c>
       <c r="R17" t="n">
         <v>128.76</v>
       </c>
       <c r="S17" t="n">
-        <v>6.7481</v>
+        <v>6.7492</v>
       </c>
       <c r="T17" t="n">
-        <v>0.93474576</v>
+        <v>0.93473564</v>
       </c>
       <c r="U17" t="n">
         <v>-128.76</v>
       </c>
       <c r="V17" t="n">
-        <v>4.1729</v>
+        <v>4.174</v>
       </c>
       <c r="W17" t="n">
-        <v>0.95912953</v>
+        <v>0.95911916</v>
       </c>
       <c r="X17" t="n">
         <v>-100</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.4605</v>
+        <v>4.4616</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.95637525</v>
+        <v>0.9563649</v>
       </c>
     </row>
     <row r="18">
@@ -2124,73 +2124,73 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>5.1872</v>
+        <v>5.3237</v>
       </c>
       <c r="E18" t="n">
-        <v>0.90145629</v>
+        <v>0.89899778</v>
       </c>
       <c r="F18" t="n">
         <v>250</v>
       </c>
       <c r="G18" t="n">
-        <v>7.6872</v>
+        <v>7.8237</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8574917399999999</v>
+        <v>0.85515314</v>
       </c>
       <c r="I18" t="n">
         <v>-250</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6872</v>
+        <v>2.8237</v>
       </c>
       <c r="K18" t="n">
-        <v>0.94767494</v>
+        <v>0.94509038</v>
       </c>
       <c r="L18" t="n">
         <v>85.94</v>
       </c>
       <c r="M18" t="n">
-        <v>6.0466</v>
+        <v>6.1831</v>
       </c>
       <c r="N18" t="n">
-        <v>0.88609428</v>
+        <v>0.88367767</v>
       </c>
       <c r="O18" t="n">
         <v>-59.38</v>
       </c>
       <c r="P18" t="n">
-        <v>4.5934</v>
+        <v>4.7299</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9122259700000001</v>
+        <v>0.9097380900000001</v>
       </c>
       <c r="R18" t="n">
         <v>47.37</v>
       </c>
       <c r="S18" t="n">
-        <v>5.6609</v>
+        <v>5.7974</v>
       </c>
       <c r="T18" t="n">
-        <v>0.89295669</v>
+        <v>0.89052136</v>
       </c>
       <c r="U18" t="n">
         <v>-47.37</v>
       </c>
       <c r="V18" t="n">
-        <v>4.7135</v>
+        <v>4.8501</v>
       </c>
       <c r="W18" t="n">
-        <v>0.91003678</v>
+        <v>0.90755487</v>
       </c>
       <c r="X18" t="n">
         <v>-100</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.1872</v>
+        <v>4.3237</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.91966691</v>
+        <v>0.91715874</v>
       </c>
     </row>
     <row r="19">
@@ -2208,73 +2208,73 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>5.1917</v>
+        <v>5.3217</v>
       </c>
       <c r="E19" t="n">
-        <v>0.85577254</v>
+        <v>0.8524403</v>
       </c>
       <c r="F19" t="n">
         <v>250</v>
       </c>
       <c r="G19" t="n">
-        <v>7.6917</v>
+        <v>7.8217</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7939374</v>
+        <v>0.79084593</v>
       </c>
       <c r="I19" t="n">
         <v>-250</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6917</v>
+        <v>2.8217</v>
       </c>
       <c r="K19" t="n">
-        <v>0.92242366</v>
+        <v>0.91883189</v>
       </c>
       <c r="L19" t="n">
         <v>116.95</v>
       </c>
       <c r="M19" t="n">
-        <v>6.3612</v>
+        <v>6.4913</v>
       </c>
       <c r="N19" t="n">
-        <v>0.82626782</v>
+        <v>0.82305047</v>
       </c>
       <c r="O19" t="n">
         <v>-92.95999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>4.2621</v>
+        <v>4.3922</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.8799738499999999</v>
+        <v>0.87654737</v>
       </c>
       <c r="R19" t="n">
         <v>17.43</v>
       </c>
       <c r="S19" t="n">
-        <v>5.3659</v>
+        <v>5.496</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8513105399999999</v>
+        <v>0.84799567</v>
       </c>
       <c r="U19" t="n">
         <v>-17.43</v>
       </c>
       <c r="V19" t="n">
-        <v>5.0174</v>
+        <v>5.1475</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8602579299999999</v>
+        <v>0.85690822</v>
       </c>
       <c r="X19" t="n">
         <v>-100</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.1917</v>
+        <v>4.3217</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.88183469</v>
+        <v>0.8784009699999999</v>
       </c>
     </row>
     <row r="20">
@@ -2292,73 +2292,73 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>5.1987</v>
+        <v>5.3169</v>
       </c>
       <c r="E20" t="n">
-        <v>0.77110321</v>
+        <v>0.76655736</v>
       </c>
       <c r="F20" t="n">
         <v>250</v>
       </c>
       <c r="G20" t="n">
-        <v>7.6987</v>
+        <v>7.8169</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6804962</v>
+        <v>0.6764845</v>
       </c>
       <c r="I20" t="n">
         <v>-250</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6987</v>
+        <v>2.8169</v>
       </c>
       <c r="K20" t="n">
-        <v>0.87377441</v>
+        <v>0.86862329</v>
       </c>
       <c r="L20" t="n">
         <v>132.56</v>
       </c>
       <c r="M20" t="n">
-        <v>6.5242</v>
+        <v>6.6425</v>
       </c>
       <c r="N20" t="n">
-        <v>0.72165233</v>
+        <v>0.717398</v>
       </c>
       <c r="O20" t="n">
         <v>-109.86</v>
       </c>
       <c r="P20" t="n">
-        <v>4.1001</v>
+        <v>4.2184</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.81464294</v>
+        <v>0.80984041</v>
       </c>
       <c r="R20" t="n">
         <v>2.36</v>
       </c>
       <c r="S20" t="n">
-        <v>5.2222</v>
+        <v>5.3405</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7701945100000001</v>
+        <v>0.76565402</v>
       </c>
       <c r="U20" t="n">
         <v>-2.36</v>
       </c>
       <c r="V20" t="n">
-        <v>5.1751</v>
+        <v>5.2933</v>
       </c>
       <c r="W20" t="n">
-        <v>0.77201299</v>
+        <v>0.76746177</v>
       </c>
       <c r="X20" t="n">
         <v>-100</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.1987</v>
+        <v>4.3169</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.81063852</v>
+        <v>0.8058596</v>
       </c>
     </row>
     <row r="21">
@@ -2376,73 +2376,73 @@
         <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>5.2036</v>
+        <v>5.3115</v>
       </c>
       <c r="E21" t="n">
-        <v>0.69471757</v>
+        <v>0.6894908</v>
       </c>
       <c r="F21" t="n">
         <v>250</v>
       </c>
       <c r="G21" t="n">
-        <v>7.7036</v>
+        <v>7.8115</v>
       </c>
       <c r="H21" t="n">
-        <v>0.58318554</v>
+        <v>0.5787979</v>
       </c>
       <c r="I21" t="n">
         <v>-250</v>
       </c>
       <c r="J21" t="n">
-        <v>2.7036</v>
+        <v>2.8115</v>
       </c>
       <c r="K21" t="n">
-        <v>0.82757968</v>
+        <v>0.82135331</v>
       </c>
       <c r="L21" t="n">
         <v>134.67</v>
       </c>
       <c r="M21" t="n">
-        <v>6.5503</v>
+        <v>6.6582</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6322195900000001</v>
+        <v>0.62746303</v>
       </c>
       <c r="O21" t="n">
         <v>-112.14</v>
       </c>
       <c r="P21" t="n">
-        <v>4.0821</v>
+        <v>4.19</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.75145013</v>
+        <v>0.74579653</v>
       </c>
       <c r="R21" t="n">
         <v>0.32</v>
       </c>
       <c r="S21" t="n">
-        <v>5.2068</v>
+        <v>5.3146</v>
       </c>
       <c r="T21" t="n">
-        <v>0.69456238</v>
+        <v>0.68933678</v>
       </c>
       <c r="U21" t="n">
         <v>-0.32</v>
       </c>
       <c r="V21" t="n">
-        <v>5.2004</v>
+        <v>5.3083</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6948728</v>
+        <v>0.68964486</v>
       </c>
       <c r="X21" t="n">
         <v>-100</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.2036</v>
+        <v>4.3115</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.74509028</v>
+        <v>0.73948453</v>
       </c>
     </row>
     <row r="22">
@@ -2460,73 +2460,73 @@
         <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>5.2083</v>
+        <v>5.3029</v>
       </c>
       <c r="E22" t="n">
-        <v>0.59402774</v>
+        <v>0.58843521</v>
       </c>
       <c r="F22" t="n">
         <v>250</v>
       </c>
       <c r="G22" t="n">
-        <v>7.7083</v>
+        <v>7.8029</v>
       </c>
       <c r="H22" t="n">
-        <v>0.46262927</v>
+        <v>0.45827381</v>
       </c>
       <c r="I22" t="n">
         <v>-250</v>
       </c>
       <c r="J22" t="n">
-        <v>2.7083</v>
+        <v>2.8029</v>
       </c>
       <c r="K22" t="n">
-        <v>0.76274671</v>
+        <v>0.75556577</v>
       </c>
       <c r="L22" t="n">
         <v>134.98</v>
       </c>
       <c r="M22" t="n">
-        <v>6.5581</v>
+        <v>6.6527</v>
       </c>
       <c r="N22" t="n">
-        <v>0.51902003</v>
+        <v>0.51413367</v>
       </c>
       <c r="O22" t="n">
         <v>-112.48</v>
       </c>
       <c r="P22" t="n">
-        <v>4.0835</v>
+        <v>4.1781</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.6647481200000001</v>
+        <v>0.65848979</v>
       </c>
       <c r="R22" t="n">
         <v>0.02</v>
       </c>
       <c r="S22" t="n">
-        <v>5.2085</v>
+        <v>5.303</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5940183</v>
+        <v>0.58842586</v>
       </c>
       <c r="U22" t="n">
         <v>-0.02</v>
       </c>
       <c r="V22" t="n">
-        <v>5.2081</v>
+        <v>5.3027</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5940371800000001</v>
+        <v>0.58844456</v>
       </c>
       <c r="X22" t="n">
         <v>-100</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.2083</v>
+        <v>4.3029</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.65650218</v>
+        <v>0.6503214899999999</v>
       </c>
     </row>
     <row r="23">
@@ -2544,73 +2544,73 @@
         <v>15</v>
       </c>
       <c r="D23" t="n">
-        <v>5.212</v>
+        <v>5.2892</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4575797</v>
+        <v>0.45231195</v>
       </c>
       <c r="F23" t="n">
         <v>250</v>
       </c>
       <c r="G23" t="n">
-        <v>7.712</v>
+        <v>7.7892</v>
       </c>
       <c r="H23" t="n">
-        <v>0.31448962</v>
+        <v>0.31086915</v>
       </c>
       <c r="I23" t="n">
         <v>-250</v>
       </c>
       <c r="J23" t="n">
-        <v>2.712</v>
+        <v>2.7892</v>
       </c>
       <c r="K23" t="n">
-        <v>0.66577454</v>
+        <v>0.65811</v>
       </c>
       <c r="L23" t="n">
         <v>135</v>
       </c>
       <c r="M23" t="n">
-        <v>6.562</v>
+        <v>6.6392</v>
       </c>
       <c r="N23" t="n">
-        <v>0.37369922</v>
+        <v>0.36939711</v>
       </c>
       <c r="O23" t="n">
         <v>-112.5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.087</v>
+        <v>4.1642</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.5416938</v>
+        <v>0.53545771</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>5.212</v>
+        <v>5.2892</v>
       </c>
       <c r="T23" t="n">
-        <v>0.45757963</v>
+        <v>0.45231187</v>
       </c>
       <c r="U23" t="n">
         <v>-0</v>
       </c>
       <c r="V23" t="n">
-        <v>5.212</v>
+        <v>5.2892</v>
       </c>
       <c r="W23" t="n">
-        <v>0.45757978</v>
+        <v>0.45231202</v>
       </c>
       <c r="X23" t="n">
         <v>-100</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.212</v>
+        <v>4.2892</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.5316317699999999</v>
+        <v>0.52551151</v>
       </c>
     </row>
     <row r="24">
@@ -2628,73 +2628,73 @@
         <v>20</v>
       </c>
       <c r="D24" t="n">
-        <v>5.2132</v>
+        <v>5.2774</v>
       </c>
       <c r="E24" t="n">
-        <v>0.35252178</v>
+        <v>0.34802439</v>
       </c>
       <c r="F24" t="n">
         <v>250</v>
       </c>
       <c r="G24" t="n">
-        <v>7.7132</v>
+        <v>7.7774</v>
       </c>
       <c r="H24" t="n">
-        <v>0.21381527</v>
+        <v>0.21108746</v>
       </c>
       <c r="I24" t="n">
         <v>-250</v>
       </c>
       <c r="J24" t="n">
-        <v>2.7132</v>
+        <v>2.7774</v>
       </c>
       <c r="K24" t="n">
-        <v>0.58121016</v>
+        <v>0.57379521</v>
       </c>
       <c r="L24" t="n">
         <v>135</v>
       </c>
       <c r="M24" t="n">
-        <v>6.5632</v>
+        <v>6.6274</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2691079</v>
+        <v>0.26567468</v>
       </c>
       <c r="O24" t="n">
         <v>-112.5</v>
       </c>
       <c r="P24" t="n">
-        <v>4.0882</v>
+        <v>4.1524</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.44147103</v>
+        <v>0.43583884</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>5.2132</v>
+        <v>5.2774</v>
       </c>
       <c r="T24" t="n">
-        <v>0.35252178</v>
+        <v>0.34802439</v>
       </c>
       <c r="U24" t="n">
         <v>-0</v>
       </c>
       <c r="V24" t="n">
-        <v>5.2132</v>
+        <v>5.2774</v>
       </c>
       <c r="W24" t="n">
-        <v>0.35252178</v>
+        <v>0.34802439</v>
       </c>
       <c r="X24" t="n">
         <v>-100</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.2132</v>
+        <v>4.2774</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.43057108</v>
+        <v>0.42507795</v>
       </c>
     </row>
     <row r="25">
@@ -2712,73 +2712,73 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>5.213</v>
+        <v>5.2598</v>
       </c>
       <c r="E25" t="n">
-        <v>0.20931663</v>
+        <v>0.20640241</v>
       </c>
       <c r="F25" t="n">
         <v>250</v>
       </c>
       <c r="G25" t="n">
-        <v>7.713</v>
+        <v>7.7598</v>
       </c>
       <c r="H25" t="n">
-        <v>0.09887417</v>
+        <v>0.0974976</v>
       </c>
       <c r="I25" t="n">
         <v>-250</v>
       </c>
       <c r="J25" t="n">
-        <v>2.713</v>
+        <v>2.7598</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4431233</v>
+        <v>0.43695391</v>
       </c>
       <c r="L25" t="n">
         <v>135</v>
       </c>
       <c r="M25" t="n">
-        <v>6.563</v>
+        <v>6.6098</v>
       </c>
       <c r="N25" t="n">
-        <v>0.13960934</v>
+        <v>0.13766562</v>
       </c>
       <c r="O25" t="n">
         <v>-112.5</v>
       </c>
       <c r="P25" t="n">
-        <v>4.088</v>
+        <v>4.1348</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.29334461</v>
+        <v>0.28926052</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>5.213</v>
+        <v>5.2598</v>
       </c>
       <c r="T25" t="n">
-        <v>0.20931663</v>
+        <v>0.20640241</v>
       </c>
       <c r="U25" t="n">
         <v>-0</v>
       </c>
       <c r="V25" t="n">
-        <v>5.213</v>
+        <v>5.2598</v>
       </c>
       <c r="W25" t="n">
-        <v>0.20931663</v>
+        <v>0.20640241</v>
       </c>
       <c r="X25" t="n">
         <v>-100</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.213</v>
+        <v>4.2598</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.28254789</v>
+        <v>0.27861412</v>
       </c>
     </row>
   </sheetData>

--- a/irrbb_calc/output/irrbb_shock_curves.xlsx
+++ b/irrbb_calc/output/irrbb_shock_curves.xlsx
@@ -1032,73 +1032,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.4616</v>
+        <v>5.4601</v>
       </c>
       <c r="E5" t="n">
-        <v>0.94684891</v>
+        <v>0.94686276</v>
       </c>
       <c r="F5" t="n">
         <v>250</v>
       </c>
       <c r="G5" t="n">
-        <v>7.9616</v>
+        <v>7.9601</v>
       </c>
       <c r="H5" t="n">
-        <v>0.92347113</v>
+        <v>0.92348464</v>
       </c>
       <c r="I5" t="n">
         <v>-250</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9616</v>
+        <v>2.9601</v>
       </c>
       <c r="K5" t="n">
-        <v>0.97081851</v>
+        <v>0.97083271</v>
       </c>
       <c r="L5" t="n">
         <v>1.64</v>
       </c>
       <c r="M5" t="n">
-        <v>5.478</v>
+        <v>5.4765</v>
       </c>
       <c r="N5" t="n">
-        <v>0.94669329</v>
+        <v>0.94670714</v>
       </c>
       <c r="O5" t="n">
         <v>31.89</v>
       </c>
       <c r="P5" t="n">
-        <v>5.7805</v>
+        <v>5.779</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.94383397</v>
+        <v>0.94384777</v>
       </c>
       <c r="R5" t="n">
         <v>128.76</v>
       </c>
       <c r="S5" t="n">
-        <v>6.7492</v>
+        <v>6.7477</v>
       </c>
       <c r="T5" t="n">
-        <v>0.93473564</v>
+        <v>0.93474932</v>
       </c>
       <c r="U5" t="n">
         <v>-128.76</v>
       </c>
       <c r="V5" t="n">
-        <v>4.174</v>
+        <v>4.1725</v>
       </c>
       <c r="W5" t="n">
-        <v>0.95911916</v>
+        <v>0.95913318</v>
       </c>
       <c r="X5" t="n">
         <v>-100</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.4616</v>
+        <v>4.4601</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9563649</v>
+        <v>0.95637889</v>
       </c>
     </row>
     <row r="6">
@@ -1116,73 +1116,73 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>5.3237</v>
+        <v>5.1392</v>
       </c>
       <c r="E6" t="n">
-        <v>0.89899778</v>
+        <v>0.90232239</v>
       </c>
       <c r="F6" t="n">
         <v>250</v>
       </c>
       <c r="G6" t="n">
-        <v>7.8237</v>
+        <v>7.6392</v>
       </c>
       <c r="H6" t="n">
-        <v>0.85515314</v>
+        <v>0.85831561</v>
       </c>
       <c r="I6" t="n">
         <v>-250</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8237</v>
+        <v>2.6392</v>
       </c>
       <c r="K6" t="n">
-        <v>0.94509038</v>
+        <v>0.9485854500000001</v>
       </c>
       <c r="L6" t="n">
         <v>85.94</v>
       </c>
       <c r="M6" t="n">
-        <v>6.1831</v>
+        <v>5.9986</v>
       </c>
       <c r="N6" t="n">
-        <v>0.88367767</v>
+        <v>0.88694563</v>
       </c>
       <c r="O6" t="n">
         <v>-59.38</v>
       </c>
       <c r="P6" t="n">
-        <v>4.7299</v>
+        <v>4.5454</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9097380900000001</v>
+        <v>0.91310242</v>
       </c>
       <c r="R6" t="n">
         <v>47.37</v>
       </c>
       <c r="S6" t="n">
-        <v>5.7974</v>
+        <v>5.6128</v>
       </c>
       <c r="T6" t="n">
-        <v>0.89052136</v>
+        <v>0.8938146300000001</v>
       </c>
       <c r="U6" t="n">
         <v>-47.37</v>
       </c>
       <c r="V6" t="n">
-        <v>4.8501</v>
+        <v>4.6655</v>
       </c>
       <c r="W6" t="n">
-        <v>0.90755487</v>
+        <v>0.91091114</v>
       </c>
       <c r="X6" t="n">
         <v>-100</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.3237</v>
+        <v>4.1392</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.91715874</v>
+        <v>0.92055052</v>
       </c>
     </row>
     <row r="7">
@@ -1200,73 +1200,73 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>5.3217</v>
+        <v>5.146</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8524403</v>
+        <v>0.85694738</v>
       </c>
       <c r="F7" t="n">
         <v>250</v>
       </c>
       <c r="G7" t="n">
-        <v>7.8217</v>
+        <v>7.646</v>
       </c>
       <c r="H7" t="n">
-        <v>0.79084593</v>
+        <v>0.79502735</v>
       </c>
       <c r="I7" t="n">
         <v>-250</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8217</v>
+        <v>2.646</v>
       </c>
       <c r="K7" t="n">
-        <v>0.91883189</v>
+        <v>0.92369</v>
       </c>
       <c r="L7" t="n">
         <v>116.95</v>
       </c>
       <c r="M7" t="n">
-        <v>6.4913</v>
+        <v>6.3155</v>
       </c>
       <c r="N7" t="n">
-        <v>0.82305047</v>
+        <v>0.82740216</v>
       </c>
       <c r="O7" t="n">
         <v>-92.95999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>4.3922</v>
+        <v>4.2164</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.87654737</v>
+        <v>0.88118192</v>
       </c>
       <c r="R7" t="n">
         <v>17.43</v>
       </c>
       <c r="S7" t="n">
-        <v>5.496</v>
+        <v>5.3202</v>
       </c>
       <c r="T7" t="n">
-        <v>0.84799567</v>
+        <v>0.85247926</v>
       </c>
       <c r="U7" t="n">
         <v>-17.43</v>
       </c>
       <c r="V7" t="n">
-        <v>5.1475</v>
+        <v>4.9717</v>
       </c>
       <c r="W7" t="n">
-        <v>0.85690822</v>
+        <v>0.86143893</v>
       </c>
       <c r="X7" t="n">
         <v>-100</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.3217</v>
+        <v>4.146</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.8784009699999999</v>
+        <v>0.88304532</v>
       </c>
     </row>
     <row r="8">
@@ -1284,73 +1284,73 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>5.3169</v>
+        <v>5.1571</v>
       </c>
       <c r="E8" t="n">
-        <v>0.76655736</v>
+        <v>0.77270812</v>
       </c>
       <c r="F8" t="n">
         <v>250</v>
       </c>
       <c r="G8" t="n">
-        <v>7.8169</v>
+        <v>7.6571</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6764845</v>
+        <v>0.68191252</v>
       </c>
       <c r="I8" t="n">
         <v>-250</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8169</v>
+        <v>2.6571</v>
       </c>
       <c r="K8" t="n">
-        <v>0.86862329</v>
+        <v>0.87559301</v>
       </c>
       <c r="L8" t="n">
         <v>132.56</v>
       </c>
       <c r="M8" t="n">
-        <v>6.6425</v>
+        <v>6.4827</v>
       </c>
       <c r="N8" t="n">
-        <v>0.717398</v>
+        <v>0.72315431</v>
       </c>
       <c r="O8" t="n">
         <v>-109.86</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2184</v>
+        <v>4.0585</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.80984041</v>
+        <v>0.81633847</v>
       </c>
       <c r="R8" t="n">
         <v>2.36</v>
       </c>
       <c r="S8" t="n">
-        <v>5.3405</v>
+        <v>5.1807</v>
       </c>
       <c r="T8" t="n">
-        <v>0.76565402</v>
+        <v>0.77179752</v>
       </c>
       <c r="U8" t="n">
         <v>-2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>5.2933</v>
+        <v>5.1335</v>
       </c>
       <c r="W8" t="n">
-        <v>0.76746177</v>
+        <v>0.77361979</v>
       </c>
       <c r="X8" t="n">
         <v>-100</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.3169</v>
+        <v>4.1571</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.8058596</v>
+        <v>0.81232571</v>
       </c>
     </row>
     <row r="9">
@@ -1368,73 +1368,73 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>5.3115</v>
+        <v>5.1656</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6894908</v>
+        <v>0.69656492</v>
       </c>
       <c r="F9" t="n">
         <v>250</v>
       </c>
       <c r="G9" t="n">
-        <v>7.8115</v>
+        <v>7.6656</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5787979</v>
+        <v>0.58473631</v>
       </c>
       <c r="I9" t="n">
         <v>-250</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8115</v>
+        <v>2.6656</v>
       </c>
       <c r="K9" t="n">
-        <v>0.82135331</v>
+        <v>0.82978032</v>
       </c>
       <c r="L9" t="n">
         <v>134.67</v>
       </c>
       <c r="M9" t="n">
-        <v>6.6582</v>
+        <v>6.5123</v>
       </c>
       <c r="N9" t="n">
-        <v>0.62746303</v>
+        <v>0.63390074</v>
       </c>
       <c r="O9" t="n">
         <v>-112.14</v>
       </c>
       <c r="P9" t="n">
-        <v>4.19</v>
+        <v>4.0442</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.74579653</v>
+        <v>0.75344834</v>
       </c>
       <c r="R9" t="n">
         <v>0.32</v>
       </c>
       <c r="S9" t="n">
-        <v>5.3146</v>
+        <v>5.1688</v>
       </c>
       <c r="T9" t="n">
-        <v>0.68933678</v>
+        <v>0.6964093099999999</v>
       </c>
       <c r="U9" t="n">
         <v>-0.32</v>
       </c>
       <c r="V9" t="n">
-        <v>5.3083</v>
+        <v>5.1624</v>
       </c>
       <c r="W9" t="n">
-        <v>0.68964486</v>
+        <v>0.69672055</v>
       </c>
       <c r="X9" t="n">
         <v>-100</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.3115</v>
+        <v>4.1656</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.73948453</v>
+        <v>0.74707157</v>
       </c>
     </row>
     <row r="10">
@@ -1452,73 +1452,73 @@
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>5.3029</v>
+        <v>5.175</v>
       </c>
       <c r="E10" t="n">
-        <v>0.58843521</v>
+        <v>0.5960069</v>
       </c>
       <c r="F10" t="n">
         <v>250</v>
       </c>
       <c r="G10" t="n">
-        <v>7.8029</v>
+        <v>7.675</v>
       </c>
       <c r="H10" t="n">
-        <v>0.45827381</v>
+        <v>0.46417064</v>
       </c>
       <c r="I10" t="n">
         <v>-250</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8029</v>
+        <v>2.675</v>
       </c>
       <c r="K10" t="n">
-        <v>0.75556577</v>
+        <v>0.76528801</v>
       </c>
       <c r="L10" t="n">
         <v>134.98</v>
       </c>
       <c r="M10" t="n">
-        <v>6.6527</v>
+        <v>6.5249</v>
       </c>
       <c r="N10" t="n">
-        <v>0.51413367</v>
+        <v>0.52074928</v>
       </c>
       <c r="O10" t="n">
         <v>-112.48</v>
       </c>
       <c r="P10" t="n">
-        <v>4.1781</v>
+        <v>4.0502</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.65848979</v>
+        <v>0.6669629</v>
       </c>
       <c r="R10" t="n">
         <v>0.02</v>
       </c>
       <c r="S10" t="n">
-        <v>5.303</v>
+        <v>5.1752</v>
       </c>
       <c r="T10" t="n">
-        <v>0.58842586</v>
+        <v>0.5959974300000001</v>
       </c>
       <c r="U10" t="n">
         <v>-0.02</v>
       </c>
       <c r="V10" t="n">
-        <v>5.3027</v>
+        <v>5.1749</v>
       </c>
       <c r="W10" t="n">
-        <v>0.58844456</v>
+        <v>0.59601637</v>
       </c>
       <c r="X10" t="n">
         <v>-100</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.3029</v>
+        <v>4.175</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.6503214899999999</v>
+        <v>0.65868949</v>
       </c>
     </row>
     <row r="11">
@@ -1536,73 +1536,73 @@
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>5.2892</v>
+        <v>5.1849</v>
       </c>
       <c r="E11" t="n">
-        <v>0.45231195</v>
+        <v>0.4594466</v>
       </c>
       <c r="F11" t="n">
         <v>250</v>
       </c>
       <c r="G11" t="n">
-        <v>7.7892</v>
+        <v>7.6849</v>
       </c>
       <c r="H11" t="n">
-        <v>0.31086915</v>
+        <v>0.31577272</v>
       </c>
       <c r="I11" t="n">
         <v>-250</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7892</v>
+        <v>2.6849</v>
       </c>
       <c r="K11" t="n">
-        <v>0.65811</v>
+        <v>0.66849086</v>
       </c>
       <c r="L11" t="n">
         <v>135</v>
       </c>
       <c r="M11" t="n">
-        <v>6.6392</v>
+        <v>6.5349</v>
       </c>
       <c r="N11" t="n">
-        <v>0.36939711</v>
+        <v>0.37522389</v>
       </c>
       <c r="O11" t="n">
         <v>-112.5</v>
       </c>
       <c r="P11" t="n">
-        <v>4.1642</v>
+        <v>4.0599</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.53545771</v>
+        <v>0.54390388</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>5.2892</v>
+        <v>5.1849</v>
       </c>
       <c r="T11" t="n">
-        <v>0.45231187</v>
+        <v>0.45944653</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>5.2892</v>
+        <v>5.1849</v>
       </c>
       <c r="W11" t="n">
-        <v>0.45231202</v>
+        <v>0.45944668</v>
       </c>
       <c r="X11" t="n">
         <v>-100</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.2892</v>
+        <v>4.1849</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.52551151</v>
+        <v>0.5338008</v>
       </c>
     </row>
     <row r="12">
@@ -1620,73 +1620,73 @@
         <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>5.2774</v>
+        <v>5.1906</v>
       </c>
       <c r="E12" t="n">
-        <v>0.34802439</v>
+        <v>0.35411702</v>
       </c>
       <c r="F12" t="n">
         <v>250</v>
       </c>
       <c r="G12" t="n">
-        <v>7.7774</v>
+        <v>7.6906</v>
       </c>
       <c r="H12" t="n">
-        <v>0.21108746</v>
+        <v>0.21478283</v>
       </c>
       <c r="I12" t="n">
         <v>-250</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7774</v>
+        <v>2.6906</v>
       </c>
       <c r="K12" t="n">
-        <v>0.57379521</v>
+        <v>0.58384026</v>
       </c>
       <c r="L12" t="n">
         <v>135</v>
       </c>
       <c r="M12" t="n">
-        <v>6.6274</v>
+        <v>6.5406</v>
       </c>
       <c r="N12" t="n">
-        <v>0.26567468</v>
+        <v>0.27032567</v>
       </c>
       <c r="O12" t="n">
         <v>-112.5</v>
       </c>
       <c r="P12" t="n">
-        <v>4.1524</v>
+        <v>4.0656</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.43583884</v>
+        <v>0.44346879</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>5.2774</v>
+        <v>5.1906</v>
       </c>
       <c r="T12" t="n">
-        <v>0.34802439</v>
+        <v>0.35411702</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.2774</v>
+        <v>5.1906</v>
       </c>
       <c r="W12" t="n">
-        <v>0.34802439</v>
+        <v>0.35411702</v>
       </c>
       <c r="X12" t="n">
         <v>-100</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.2774</v>
+        <v>4.1906</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.42507795</v>
+        <v>0.43251951</v>
       </c>
     </row>
     <row r="13">
@@ -1704,73 +1704,73 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2598</v>
+        <v>5.1966</v>
       </c>
       <c r="E13" t="n">
-        <v>0.20640241</v>
+        <v>0.21035113</v>
       </c>
       <c r="F13" t="n">
         <v>250</v>
       </c>
       <c r="G13" t="n">
-        <v>7.7598</v>
+        <v>7.6966</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0974976</v>
+        <v>0.09936283999999999</v>
       </c>
       <c r="I13" t="n">
         <v>-250</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7598</v>
+        <v>2.6966</v>
       </c>
       <c r="K13" t="n">
-        <v>0.43695391</v>
+        <v>0.44531335</v>
       </c>
       <c r="L13" t="n">
         <v>135</v>
       </c>
       <c r="M13" t="n">
-        <v>6.6098</v>
+        <v>6.5466</v>
       </c>
       <c r="N13" t="n">
-        <v>0.13766562</v>
+        <v>0.14029933</v>
       </c>
       <c r="O13" t="n">
         <v>-112.5</v>
       </c>
       <c r="P13" t="n">
-        <v>4.1348</v>
+        <v>4.0716</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.28926052</v>
+        <v>0.29479441</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>5.2598</v>
+        <v>5.1966</v>
       </c>
       <c r="T13" t="n">
-        <v>0.20640241</v>
+        <v>0.21035113</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>5.2598</v>
+        <v>5.1966</v>
       </c>
       <c r="W13" t="n">
-        <v>0.20640241</v>
+        <v>0.21035113</v>
       </c>
       <c r="X13" t="n">
         <v>-100</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.2598</v>
+        <v>4.1966</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.27861412</v>
+        <v>0.28394433</v>
       </c>
     </row>
     <row r="14">
@@ -2040,73 +2040,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.4616</v>
+        <v>5.4601</v>
       </c>
       <c r="E17" t="n">
-        <v>0.94684891</v>
+        <v>0.94686276</v>
       </c>
       <c r="F17" t="n">
         <v>250</v>
       </c>
       <c r="G17" t="n">
-        <v>7.9616</v>
+        <v>7.9601</v>
       </c>
       <c r="H17" t="n">
-        <v>0.92347113</v>
+        <v>0.92348464</v>
       </c>
       <c r="I17" t="n">
         <v>-250</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9616</v>
+        <v>2.9601</v>
       </c>
       <c r="K17" t="n">
-        <v>0.97081851</v>
+        <v>0.97083271</v>
       </c>
       <c r="L17" t="n">
         <v>1.64</v>
       </c>
       <c r="M17" t="n">
-        <v>5.478</v>
+        <v>5.4765</v>
       </c>
       <c r="N17" t="n">
-        <v>0.94669329</v>
+        <v>0.94670714</v>
       </c>
       <c r="O17" t="n">
         <v>31.89</v>
       </c>
       <c r="P17" t="n">
-        <v>5.7805</v>
+        <v>5.779</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.94383397</v>
+        <v>0.94384777</v>
       </c>
       <c r="R17" t="n">
         <v>128.76</v>
       </c>
       <c r="S17" t="n">
-        <v>6.7492</v>
+        <v>6.7477</v>
       </c>
       <c r="T17" t="n">
-        <v>0.93473564</v>
+        <v>0.93474932</v>
       </c>
       <c r="U17" t="n">
         <v>-128.76</v>
       </c>
       <c r="V17" t="n">
-        <v>4.174</v>
+        <v>4.1725</v>
       </c>
       <c r="W17" t="n">
-        <v>0.95911916</v>
+        <v>0.95913318</v>
       </c>
       <c r="X17" t="n">
         <v>-100</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.4616</v>
+        <v>4.4601</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.9563649</v>
+        <v>0.95637889</v>
       </c>
     </row>
     <row r="18">
@@ -2124,73 +2124,73 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>5.3237</v>
+        <v>5.1392</v>
       </c>
       <c r="E18" t="n">
-        <v>0.89899778</v>
+        <v>0.90232239</v>
       </c>
       <c r="F18" t="n">
         <v>250</v>
       </c>
       <c r="G18" t="n">
-        <v>7.8237</v>
+        <v>7.6392</v>
       </c>
       <c r="H18" t="n">
-        <v>0.85515314</v>
+        <v>0.85831561</v>
       </c>
       <c r="I18" t="n">
         <v>-250</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8237</v>
+        <v>2.6392</v>
       </c>
       <c r="K18" t="n">
-        <v>0.94509038</v>
+        <v>0.9485854500000001</v>
       </c>
       <c r="L18" t="n">
         <v>85.94</v>
       </c>
       <c r="M18" t="n">
-        <v>6.1831</v>
+        <v>5.9986</v>
       </c>
       <c r="N18" t="n">
-        <v>0.88367767</v>
+        <v>0.88694563</v>
       </c>
       <c r="O18" t="n">
         <v>-59.38</v>
       </c>
       <c r="P18" t="n">
-        <v>4.7299</v>
+        <v>4.5454</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9097380900000001</v>
+        <v>0.91310242</v>
       </c>
       <c r="R18" t="n">
         <v>47.37</v>
       </c>
       <c r="S18" t="n">
-        <v>5.7974</v>
+        <v>5.6128</v>
       </c>
       <c r="T18" t="n">
-        <v>0.89052136</v>
+        <v>0.8938146300000001</v>
       </c>
       <c r="U18" t="n">
         <v>-47.37</v>
       </c>
       <c r="V18" t="n">
-        <v>4.8501</v>
+        <v>4.6655</v>
       </c>
       <c r="W18" t="n">
-        <v>0.90755487</v>
+        <v>0.91091114</v>
       </c>
       <c r="X18" t="n">
         <v>-100</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.3237</v>
+        <v>4.1392</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.91715874</v>
+        <v>0.92055052</v>
       </c>
     </row>
     <row r="19">
@@ -2208,73 +2208,73 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>5.3217</v>
+        <v>5.146</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8524403</v>
+        <v>0.85694738</v>
       </c>
       <c r="F19" t="n">
         <v>250</v>
       </c>
       <c r="G19" t="n">
-        <v>7.8217</v>
+        <v>7.646</v>
       </c>
       <c r="H19" t="n">
-        <v>0.79084593</v>
+        <v>0.79502735</v>
       </c>
       <c r="I19" t="n">
         <v>-250</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8217</v>
+        <v>2.646</v>
       </c>
       <c r="K19" t="n">
-        <v>0.91883189</v>
+        <v>0.92369</v>
       </c>
       <c r="L19" t="n">
         <v>116.95</v>
       </c>
       <c r="M19" t="n">
-        <v>6.4913</v>
+        <v>6.3155</v>
       </c>
       <c r="N19" t="n">
-        <v>0.82305047</v>
+        <v>0.82740216</v>
       </c>
       <c r="O19" t="n">
         <v>-92.95999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>4.3922</v>
+        <v>4.2164</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.87654737</v>
+        <v>0.88118192</v>
       </c>
       <c r="R19" t="n">
         <v>17.43</v>
       </c>
       <c r="S19" t="n">
-        <v>5.496</v>
+        <v>5.3202</v>
       </c>
       <c r="T19" t="n">
-        <v>0.84799567</v>
+        <v>0.85247926</v>
       </c>
       <c r="U19" t="n">
         <v>-17.43</v>
       </c>
       <c r="V19" t="n">
-        <v>5.1475</v>
+        <v>4.9717</v>
       </c>
       <c r="W19" t="n">
-        <v>0.85690822</v>
+        <v>0.86143893</v>
       </c>
       <c r="X19" t="n">
         <v>-100</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.3217</v>
+        <v>4.146</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.8784009699999999</v>
+        <v>0.88304532</v>
       </c>
     </row>
     <row r="20">
@@ -2292,73 +2292,73 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>5.3169</v>
+        <v>5.1571</v>
       </c>
       <c r="E20" t="n">
-        <v>0.76655736</v>
+        <v>0.77270812</v>
       </c>
       <c r="F20" t="n">
         <v>250</v>
       </c>
       <c r="G20" t="n">
-        <v>7.8169</v>
+        <v>7.6571</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6764845</v>
+        <v>0.68191252</v>
       </c>
       <c r="I20" t="n">
         <v>-250</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8169</v>
+        <v>2.6571</v>
       </c>
       <c r="K20" t="n">
-        <v>0.86862329</v>
+        <v>0.87559301</v>
       </c>
       <c r="L20" t="n">
         <v>132.56</v>
       </c>
       <c r="M20" t="n">
-        <v>6.6425</v>
+        <v>6.4827</v>
       </c>
       <c r="N20" t="n">
-        <v>0.717398</v>
+        <v>0.72315431</v>
       </c>
       <c r="O20" t="n">
         <v>-109.86</v>
       </c>
       <c r="P20" t="n">
-        <v>4.2184</v>
+        <v>4.0585</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.80984041</v>
+        <v>0.81633847</v>
       </c>
       <c r="R20" t="n">
         <v>2.36</v>
       </c>
       <c r="S20" t="n">
-        <v>5.3405</v>
+        <v>5.1807</v>
       </c>
       <c r="T20" t="n">
-        <v>0.76565402</v>
+        <v>0.77179752</v>
       </c>
       <c r="U20" t="n">
         <v>-2.36</v>
       </c>
       <c r="V20" t="n">
-        <v>5.2933</v>
+        <v>5.1335</v>
       </c>
       <c r="W20" t="n">
-        <v>0.76746177</v>
+        <v>0.77361979</v>
       </c>
       <c r="X20" t="n">
         <v>-100</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.3169</v>
+        <v>4.1571</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.8058596</v>
+        <v>0.81232571</v>
       </c>
     </row>
     <row r="21">
@@ -2376,73 +2376,73 @@
         <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>5.3115</v>
+        <v>5.1656</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6894908</v>
+        <v>0.69656492</v>
       </c>
       <c r="F21" t="n">
         <v>250</v>
       </c>
       <c r="G21" t="n">
-        <v>7.8115</v>
+        <v>7.6656</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5787979</v>
+        <v>0.58473631</v>
       </c>
       <c r="I21" t="n">
         <v>-250</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8115</v>
+        <v>2.6656</v>
       </c>
       <c r="K21" t="n">
-        <v>0.82135331</v>
+        <v>0.82978032</v>
       </c>
       <c r="L21" t="n">
         <v>134.67</v>
       </c>
       <c r="M21" t="n">
-        <v>6.6582</v>
+        <v>6.5123</v>
       </c>
       <c r="N21" t="n">
-        <v>0.62746303</v>
+        <v>0.63390074</v>
       </c>
       <c r="O21" t="n">
         <v>-112.14</v>
       </c>
       <c r="P21" t="n">
-        <v>4.19</v>
+        <v>4.0442</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.74579653</v>
+        <v>0.75344834</v>
       </c>
       <c r="R21" t="n">
         <v>0.32</v>
       </c>
       <c r="S21" t="n">
-        <v>5.3146</v>
+        <v>5.1688</v>
       </c>
       <c r="T21" t="n">
-        <v>0.68933678</v>
+        <v>0.6964093099999999</v>
       </c>
       <c r="U21" t="n">
         <v>-0.32</v>
       </c>
       <c r="V21" t="n">
-        <v>5.3083</v>
+        <v>5.1624</v>
       </c>
       <c r="W21" t="n">
-        <v>0.68964486</v>
+        <v>0.69672055</v>
       </c>
       <c r="X21" t="n">
         <v>-100</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.3115</v>
+        <v>4.1656</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.73948453</v>
+        <v>0.74707157</v>
       </c>
     </row>
     <row r="22">
@@ -2460,73 +2460,73 @@
         <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>5.3029</v>
+        <v>5.175</v>
       </c>
       <c r="E22" t="n">
-        <v>0.58843521</v>
+        <v>0.5960069</v>
       </c>
       <c r="F22" t="n">
         <v>250</v>
       </c>
       <c r="G22" t="n">
-        <v>7.8029</v>
+        <v>7.675</v>
       </c>
       <c r="H22" t="n">
-        <v>0.45827381</v>
+        <v>0.46417064</v>
       </c>
       <c r="I22" t="n">
         <v>-250</v>
       </c>
       <c r="J22" t="n">
-        <v>2.8029</v>
+        <v>2.675</v>
       </c>
       <c r="K22" t="n">
-        <v>0.75556577</v>
+        <v>0.76528801</v>
       </c>
       <c r="L22" t="n">
         <v>134.98</v>
       </c>
       <c r="M22" t="n">
-        <v>6.6527</v>
+        <v>6.5249</v>
       </c>
       <c r="N22" t="n">
-        <v>0.51413367</v>
+        <v>0.52074928</v>
       </c>
       <c r="O22" t="n">
         <v>-112.48</v>
       </c>
       <c r="P22" t="n">
-        <v>4.1781</v>
+        <v>4.0502</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.65848979</v>
+        <v>0.6669629</v>
       </c>
       <c r="R22" t="n">
         <v>0.02</v>
       </c>
       <c r="S22" t="n">
-        <v>5.303</v>
+        <v>5.1752</v>
       </c>
       <c r="T22" t="n">
-        <v>0.58842586</v>
+        <v>0.5959974300000001</v>
       </c>
       <c r="U22" t="n">
         <v>-0.02</v>
       </c>
       <c r="V22" t="n">
-        <v>5.3027</v>
+        <v>5.1749</v>
       </c>
       <c r="W22" t="n">
-        <v>0.58844456</v>
+        <v>0.59601637</v>
       </c>
       <c r="X22" t="n">
         <v>-100</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.3029</v>
+        <v>4.175</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.6503214899999999</v>
+        <v>0.65868949</v>
       </c>
     </row>
     <row r="23">
@@ -2544,73 +2544,73 @@
         <v>15</v>
       </c>
       <c r="D23" t="n">
-        <v>5.2892</v>
+        <v>5.1849</v>
       </c>
       <c r="E23" t="n">
-        <v>0.45231195</v>
+        <v>0.4594466</v>
       </c>
       <c r="F23" t="n">
         <v>250</v>
       </c>
       <c r="G23" t="n">
-        <v>7.7892</v>
+        <v>7.6849</v>
       </c>
       <c r="H23" t="n">
-        <v>0.31086915</v>
+        <v>0.31577272</v>
       </c>
       <c r="I23" t="n">
         <v>-250</v>
       </c>
       <c r="J23" t="n">
-        <v>2.7892</v>
+        <v>2.6849</v>
       </c>
       <c r="K23" t="n">
-        <v>0.65811</v>
+        <v>0.66849086</v>
       </c>
       <c r="L23" t="n">
         <v>135</v>
       </c>
       <c r="M23" t="n">
-        <v>6.6392</v>
+        <v>6.5349</v>
       </c>
       <c r="N23" t="n">
-        <v>0.36939711</v>
+        <v>0.37522389</v>
       </c>
       <c r="O23" t="n">
         <v>-112.5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.1642</v>
+        <v>4.0599</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.53545771</v>
+        <v>0.54390388</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>5.2892</v>
+        <v>5.1849</v>
       </c>
       <c r="T23" t="n">
-        <v>0.45231187</v>
+        <v>0.45944653</v>
       </c>
       <c r="U23" t="n">
         <v>-0</v>
       </c>
       <c r="V23" t="n">
-        <v>5.2892</v>
+        <v>5.1849</v>
       </c>
       <c r="W23" t="n">
-        <v>0.45231202</v>
+        <v>0.45944668</v>
       </c>
       <c r="X23" t="n">
         <v>-100</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.2892</v>
+        <v>4.1849</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.52551151</v>
+        <v>0.5338008</v>
       </c>
     </row>
     <row r="24">
@@ -2628,73 +2628,73 @@
         <v>20</v>
       </c>
       <c r="D24" t="n">
-        <v>5.2774</v>
+        <v>5.1906</v>
       </c>
       <c r="E24" t="n">
-        <v>0.34802439</v>
+        <v>0.35411702</v>
       </c>
       <c r="F24" t="n">
         <v>250</v>
       </c>
       <c r="G24" t="n">
-        <v>7.7774</v>
+        <v>7.6906</v>
       </c>
       <c r="H24" t="n">
-        <v>0.21108746</v>
+        <v>0.21478283</v>
       </c>
       <c r="I24" t="n">
         <v>-250</v>
       </c>
       <c r="J24" t="n">
-        <v>2.7774</v>
+        <v>2.6906</v>
       </c>
       <c r="K24" t="n">
-        <v>0.57379521</v>
+        <v>0.58384026</v>
       </c>
       <c r="L24" t="n">
         <v>135</v>
       </c>
       <c r="M24" t="n">
-        <v>6.6274</v>
+        <v>6.5406</v>
       </c>
       <c r="N24" t="n">
-        <v>0.26567468</v>
+        <v>0.27032567</v>
       </c>
       <c r="O24" t="n">
         <v>-112.5</v>
       </c>
       <c r="P24" t="n">
-        <v>4.1524</v>
+        <v>4.0656</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.43583884</v>
+        <v>0.44346879</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>5.2774</v>
+        <v>5.1906</v>
       </c>
       <c r="T24" t="n">
-        <v>0.34802439</v>
+        <v>0.35411702</v>
       </c>
       <c r="U24" t="n">
         <v>-0</v>
       </c>
       <c r="V24" t="n">
-        <v>5.2774</v>
+        <v>5.1906</v>
       </c>
       <c r="W24" t="n">
-        <v>0.34802439</v>
+        <v>0.35411702</v>
       </c>
       <c r="X24" t="n">
         <v>-100</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.2774</v>
+        <v>4.1906</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.42507795</v>
+        <v>0.43251951</v>
       </c>
     </row>
     <row r="25">
@@ -2712,73 +2712,73 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>5.2598</v>
+        <v>5.1966</v>
       </c>
       <c r="E25" t="n">
-        <v>0.20640241</v>
+        <v>0.21035113</v>
       </c>
       <c r="F25" t="n">
         <v>250</v>
       </c>
       <c r="G25" t="n">
-        <v>7.7598</v>
+        <v>7.6966</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0974976</v>
+        <v>0.09936283999999999</v>
       </c>
       <c r="I25" t="n">
         <v>-250</v>
       </c>
       <c r="J25" t="n">
-        <v>2.7598</v>
+        <v>2.6966</v>
       </c>
       <c r="K25" t="n">
-        <v>0.43695391</v>
+        <v>0.44531335</v>
       </c>
       <c r="L25" t="n">
         <v>135</v>
       </c>
       <c r="M25" t="n">
-        <v>6.6098</v>
+        <v>6.5466</v>
       </c>
       <c r="N25" t="n">
-        <v>0.13766562</v>
+        <v>0.14029933</v>
       </c>
       <c r="O25" t="n">
         <v>-112.5</v>
       </c>
       <c r="P25" t="n">
-        <v>4.1348</v>
+        <v>4.0716</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.28926052</v>
+        <v>0.29479441</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>5.2598</v>
+        <v>5.1966</v>
       </c>
       <c r="T25" t="n">
-        <v>0.20640241</v>
+        <v>0.21035113</v>
       </c>
       <c r="U25" t="n">
         <v>-0</v>
       </c>
       <c r="V25" t="n">
-        <v>5.2598</v>
+        <v>5.1966</v>
       </c>
       <c r="W25" t="n">
-        <v>0.20640241</v>
+        <v>0.21035113</v>
       </c>
       <c r="X25" t="n">
         <v>-100</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.2598</v>
+        <v>4.1966</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.27861412</v>
+        <v>0.28394433</v>
       </c>
     </row>
   </sheetData>
